--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T10:41:09+00:00</t>
+    <t>2026-08-27T11:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:11:54+00:00</t>
+    <t>2026-08-27T11:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:29:36+00:00</t>
+    <t>2026-08-27T12:06:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:06:00+00:00</t>
+    <t>2026-08-27T15:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:31:43+00:00</t>
+    <t>2026-08-27T15:57:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:57:15+00:00</t>
+    <t>2026-08-28T06:12:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:12:02+00:00</t>
+    <t>2026-08-28T06:31:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:31:49+00:00</t>
+    <t>2026-08-28T06:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$178</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6084" uniqueCount="663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6118" uniqueCount="667">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:24:31+00:00</t>
+    <t>2026-08-28T07:40:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1028,8 +1028,22 @@
     <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this.resolve()}
+</t>
+  </si>
+  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>Procedure.basedOn:tumorkonferenz</t>
+  </si>
+  <si>
+    <t>tumorkonferenz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-pr-onko-tumorkonferenz)
+</t>
   </si>
   <si>
     <t>Procedure.partOf</t>
@@ -2391,7 +2405,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL177"/>
+  <dimension ref="A1:AL178"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.1015625" customWidth="true" bestFit="true"/>
@@ -8373,7 +8387,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>320</v>
       </c>
@@ -8448,16 +8462,14 @@
         <v>75</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="AC56" s="2"/>
       <c r="AD56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>320</v>
@@ -8472,7 +8484,7 @@
         <v>97</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>75</v>
@@ -8483,21 +8495,23 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="D57" t="s" s="2">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>86</v>
@@ -8509,16 +8523,16 @@
         <v>86</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8568,7 +8582,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8580,7 +8594,7 @@
         <v>97</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>75</v>
@@ -8591,42 +8605,42 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>75</v>
+        <v>332</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>86</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>161</v>
+        <v>333</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>10</v>
+        <v>334</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8652,13 +8666,13 @@
         <v>75</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>217</v>
+        <v>75</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>336</v>
+        <v>75</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>337</v>
+        <v>75</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>75</v>
@@ -8676,19 +8690,19 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>98</v>
+        <v>327</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>75</v>
@@ -8697,44 +8711,44 @@
         <v>75</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>339</v>
+        <v>75</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>214</v>
+        <v>161</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>340</v>
+        <v>10</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8760,13 +8774,13 @@
         <v>75</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>151</v>
+        <v>217</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>75</v>
@@ -8784,10 +8798,10 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>85</v>
@@ -8805,16 +8819,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>75</v>
+        <v>343</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8824,7 +8838,7 @@
         <v>85</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>75</v>
@@ -8836,13 +8850,13 @@
         <v>214</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8871,10 +8885,10 @@
         <v>151</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>75</v>
@@ -8892,7 +8906,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8913,12 +8927,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8932,24 +8946,26 @@
         <v>85</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>100</v>
+        <v>214</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>101</v>
+        <v>350</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>75</v>
@@ -8974,13 +8990,13 @@
         <v>75</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>75</v>
+        <v>353</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>75</v>
+        <v>354</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>75</v>
@@ -8998,7 +9014,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>103</v>
+        <v>349</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -9007,10 +9023,10 @@
         <v>85</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>75</v>
@@ -9021,21 +9037,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>75</v>
@@ -9047,17 +9063,15 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>75</v>
@@ -9094,31 +9108,31 @@
         <v>75</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>75</v>
@@ -9129,14 +9143,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9152,23 +9166,21 @@
         <v>75</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>226</v>
+        <v>107</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>227</v>
+        <v>108</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>75</v>
       </c>
@@ -9204,9 +9216,11 @@
         <v>75</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AC63" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="AD63" t="s" s="2">
         <v>75</v>
       </c>
@@ -9214,7 +9228,7 @@
         <v>112</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>230</v>
+        <v>113</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9226,7 +9240,7 @@
         <v>97</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>75</v>
@@ -9235,16 +9249,14 @@
         <v>75</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>75</v>
       </c>
@@ -9253,10 +9265,10 @@
         <v>76</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>75</v>
@@ -9268,10 +9280,10 @@
         <v>139</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>357</v>
+        <v>226</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>358</v>
+        <v>227</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>228</v>
@@ -9287,7 +9299,7 @@
         <v>75</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>359</v>
+        <v>75</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>75</v>
@@ -9302,26 +9314,26 @@
         <v>75</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>360</v>
+        <v>75</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="AC64" s="2"/>
       <c r="AD64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>230</v>
@@ -9345,14 +9357,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="C65" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="D65" t="s" s="2">
         <v>75</v>
       </c>
@@ -9364,25 +9378,29 @@
         <v>85</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>101</v>
+        <v>361</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>75</v>
       </c>
@@ -9391,7 +9409,7 @@
         <v>75</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>75</v>
+        <v>363</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>75</v>
@@ -9406,13 +9424,11 @@
         <v>75</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>75</v>
+        <v>364</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>75</v>
@@ -9430,19 +9446,19 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>75</v>
@@ -9453,21 +9469,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>75</v>
@@ -9479,17 +9495,15 @@
         <v>75</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>75</v>
@@ -9526,31 +9540,31 @@
         <v>75</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>75</v>
@@ -9559,48 +9573,46 @@
         <v>75</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>237</v>
+        <v>107</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>75</v>
       </c>
@@ -9636,31 +9648,31 @@
         <v>75</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>75</v>
@@ -9669,12 +9681,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9682,13 +9694,13 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>75</v>
@@ -9697,18 +9709,20 @@
         <v>86</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>75</v>
       </c>
@@ -9756,7 +9770,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9777,12 +9791,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9790,13 +9804,13 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>75</v>
@@ -9805,20 +9819,18 @@
         <v>86</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>75</v>
       </c>
@@ -9866,7 +9878,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9887,12 +9899,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9900,13 +9912,13 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>75</v>
@@ -9915,19 +9927,19 @@
         <v>86</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>75</v>
@@ -9976,7 +9988,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9999,10 +10011,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10025,19 +10037,19 @@
         <v>86</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>267</v>
+        <v>375</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>75</v>
@@ -10086,7 +10098,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10109,10 +10121,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10135,19 +10147,19 @@
         <v>86</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>75</v>
@@ -10196,7 +10208,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10217,26 +10229,26 @@
         <v>75</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>378</v>
+        <v>75</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>75</v>
@@ -10245,19 +10257,19 @@
         <v>86</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>214</v>
+        <v>100</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>379</v>
+        <v>272</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>380</v>
+        <v>273</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>348</v>
+        <v>274</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>381</v>
+        <v>275</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>75</v>
@@ -10282,13 +10294,13 @@
         <v>75</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>382</v>
+        <v>75</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>383</v>
+        <v>75</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>75</v>
@@ -10306,7 +10318,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>377</v>
+        <v>276</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -10318,7 +10330,7 @@
         <v>97</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>384</v>
+        <v>98</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>75</v>
@@ -10327,44 +10339,48 @@
         <v>75</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>75</v>
+        <v>382</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>100</v>
+        <v>214</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>101</v>
+        <v>383</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>75</v>
       </c>
@@ -10388,13 +10404,13 @@
         <v>75</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>75</v>
+        <v>386</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>75</v>
+        <v>387</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>75</v>
@@ -10412,7 +10428,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>103</v>
+        <v>381</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -10421,10 +10437,10 @@
         <v>85</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>75</v>
+        <v>388</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>75</v>
@@ -10435,21 +10451,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>75</v>
@@ -10461,17 +10477,15 @@
         <v>75</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>75</v>
@@ -10508,31 +10522,31 @@
         <v>75</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>75</v>
@@ -10543,46 +10557,44 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>226</v>
+        <v>107</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>227</v>
+        <v>108</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>75</v>
       </c>
@@ -10618,9 +10630,11 @@
         <v>75</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AC76" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="AD76" t="s" s="2">
         <v>75</v>
       </c>
@@ -10628,7 +10642,7 @@
         <v>112</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>230</v>
+        <v>113</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -10640,34 +10654,32 @@
         <v>97</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>389</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>86</v>
@@ -10679,16 +10691,16 @@
         <v>86</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>390</v>
+        <v>139</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>391</v>
+        <v>226</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>392</v>
+        <v>227</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>393</v>
+        <v>228</v>
       </c>
       <c r="O77" t="s" s="2">
         <v>229</v>
@@ -10701,7 +10713,7 @@
         <v>75</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>394</v>
+        <v>75</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>75</v>
@@ -10716,26 +10728,26 @@
         <v>75</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="Y77" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z77" t="s" s="2">
-        <v>395</v>
+        <v>75</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="AC77" s="2"/>
       <c r="AD77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>230</v>
@@ -10753,20 +10765,22 @@
         <v>98</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="D78" t="s" s="2">
         <v>75</v>
       </c>
@@ -10778,25 +10792,29 @@
         <v>85</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>100</v>
+        <v>394</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>101</v>
+        <v>395</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>75</v>
       </c>
@@ -10805,7 +10823,7 @@
         <v>75</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>75</v>
+        <v>398</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>75</v>
@@ -10820,13 +10838,11 @@
         <v>75</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>75</v>
+        <v>399</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>75</v>
@@ -10844,19 +10860,19 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>75</v>
@@ -10867,21 +10883,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>75</v>
@@ -10893,17 +10909,15 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>75</v>
@@ -10940,31 +10954,31 @@
         <v>75</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>75</v>
@@ -10973,16 +10987,14 @@
         <v>75</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="C80" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>105</v>
       </c>
@@ -10991,10 +11003,10 @@
         <v>76</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>75</v>
@@ -11003,13 +11015,13 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>402</v>
+        <v>106</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>403</v>
+        <v>107</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>404</v>
+        <v>108</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>109</v>
@@ -11050,16 +11062,16 @@
         <v>75</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>113</v>
@@ -11085,18 +11097,20 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="C81" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="B81" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>85</v>
@@ -11108,29 +11122,27 @@
         <v>75</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>127</v>
+        <v>406</v>
       </c>
       <c r="L81" t="s" s="2">
         <v>407</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>238</v>
+        <v>408</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>408</v>
+        <v>75</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>75</v>
@@ -11172,19 +11184,19 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>75</v>
@@ -11221,24 +11233,26 @@
         <v>86</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L82" t="s" s="2">
         <v>411</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>412</v>
+        <v>238</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>75</v>
+        <v>412</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>75</v>
@@ -11280,7 +11294,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -11298,15 +11312,15 @@
         <v>75</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>413</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B83" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11329,20 +11343,18 @@
         <v>86</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="M83" t="s" s="2">
-        <v>252</v>
-      </c>
       <c r="N83" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>75</v>
       </c>
@@ -11354,7 +11366,7 @@
         <v>75</v>
       </c>
       <c r="T83" t="s" s="2">
-        <v>417</v>
+        <v>75</v>
       </c>
       <c r="U83" t="s" s="2">
         <v>75</v>
@@ -11390,7 +11402,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -11402,21 +11414,21 @@
         <v>97</v>
       </c>
       <c r="AJ83" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AK83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL83" t="s" s="2">
+      <c r="B84" t="s" s="2">
         <v>419</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11424,13 +11436,13 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>75</v>
@@ -11439,19 +11451,19 @@
         <v>86</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>258</v>
+        <v>420</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>75</v>
@@ -11464,7 +11476,7 @@
         <v>75</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>75</v>
+        <v>421</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>75</v>
@@ -11500,7 +11512,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -11512,21 +11524,21 @@
         <v>97</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>98</v>
+        <v>422</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>75</v>
+        <v>423</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11549,19 +11561,19 @@
         <v>86</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>267</v>
+        <v>375</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>75</v>
@@ -11610,7 +11622,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -11631,16 +11643,14 @@
         <v>75</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>75</v>
       </c>
@@ -11652,7 +11662,7 @@
         <v>85</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>75</v>
@@ -11661,19 +11671,19 @@
         <v>86</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>139</v>
+        <v>264</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>357</v>
+        <v>265</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>358</v>
+        <v>266</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>228</v>
+        <v>267</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>229</v>
+        <v>268</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>75</v>
@@ -11683,7 +11693,7 @@
         <v>75</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>359</v>
+        <v>75</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>75</v>
@@ -11698,11 +11708,13 @@
         <v>75</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="Y86" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z86" t="s" s="2">
-        <v>425</v>
+        <v>75</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>75</v>
@@ -11720,13 +11732,13 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>230</v>
+        <v>269</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>97</v>
@@ -11741,14 +11753,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="C87" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="D87" t="s" s="2">
         <v>75</v>
       </c>
@@ -11760,25 +11774,29 @@
         <v>85</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>101</v>
+        <v>361</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>75</v>
       </c>
@@ -11787,7 +11805,7 @@
         <v>75</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>75</v>
+        <v>363</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>75</v>
@@ -11802,13 +11820,11 @@
         <v>75</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="Y87" s="2"/>
       <c r="Z87" t="s" s="2">
-        <v>75</v>
+        <v>429</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>75</v>
@@ -11826,19 +11842,19 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>75</v>
@@ -11849,21 +11865,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>75</v>
@@ -11875,17 +11891,15 @@
         <v>75</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>75</v>
@@ -11922,31 +11936,31 @@
         <v>75</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>75</v>
@@ -11955,48 +11969,46 @@
         <v>75</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>237</v>
+        <v>107</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>75</v>
       </c>
@@ -12032,31 +12044,31 @@
         <v>75</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>75</v>
@@ -12065,9 +12077,9 @@
         <v>75</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>410</v>
@@ -12078,13 +12090,13 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>75</v>
@@ -12093,18 +12105,20 @@
         <v>86</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>75</v>
       </c>
@@ -12152,7 +12166,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -12173,12 +12187,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12186,13 +12200,13 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>75</v>
@@ -12201,20 +12215,18 @@
         <v>86</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>75</v>
       </c>
@@ -12262,7 +12274,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -12283,12 +12295,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12296,13 +12308,13 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>75</v>
@@ -12311,19 +12323,19 @@
         <v>86</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>75</v>
@@ -12372,7 +12384,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -12395,10 +12407,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12421,19 +12433,19 @@
         <v>86</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>267</v>
+        <v>375</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>75</v>
@@ -12482,7 +12494,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -12505,10 +12517,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12531,19 +12543,19 @@
         <v>86</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>75</v>
@@ -12592,7 +12604,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -12613,26 +12625,26 @@
         <v>75</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>435</v>
+        <v>75</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>75</v>
@@ -12641,18 +12653,20 @@
         <v>86</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>436</v>
+        <v>100</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>437</v>
+        <v>272</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>438</v>
+        <v>273</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>75</v>
       </c>
@@ -12700,10 +12714,10 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>434</v>
+        <v>276</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>85</v>
@@ -12712,7 +12726,7 @@
         <v>97</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>326</v>
+        <v>98</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>75</v>
@@ -12723,18 +12737,18 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>75</v>
+        <v>439</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>85</v>
@@ -12758,7 +12772,7 @@
         <v>442</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>443</v>
+        <v>325</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12808,10 +12822,10 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>85</v>
@@ -12820,7 +12834,7 @@
         <v>97</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>75</v>
@@ -12829,12 +12843,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12842,7 +12856,7 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>85</v>
@@ -12857,16 +12871,16 @@
         <v>86</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -12904,17 +12918,19 @@
         <v>75</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AC97" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD97" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>450</v>
+        <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -12926,7 +12942,7 @@
         <v>97</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>98</v>
+        <v>327</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>75</v>
@@ -12937,26 +12953,24 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="C98" t="s" s="2">
-        <v>452</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>75</v>
@@ -12965,16 +12979,16 @@
         <v>86</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13012,19 +13026,17 @@
         <v>75</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="AC98" s="2"/>
       <c r="AD98" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>75</v>
+        <v>454</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -13042,18 +13054,18 @@
         <v>75</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>455</v>
+        <v>75</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="C99" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>75</v>
@@ -13075,16 +13087,16 @@
         <v>86</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="L99" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>460</v>
-      </c>
       <c r="N99" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13134,7 +13146,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -13152,17 +13164,19 @@
         <v>75</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>75</v>
+        <v>459</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="C100" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="B100" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
         <v>75</v>
       </c>
@@ -13192,7 +13206,7 @@
         <v>464</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>325</v>
+        <v>452</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13242,7 +13256,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -13254,7 +13268,7 @@
         <v>97</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>326</v>
+        <v>98</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>75</v>
@@ -13291,13 +13305,13 @@
         <v>86</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>325</v>
@@ -13362,7 +13376,7 @@
         <v>97</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>75</v>
@@ -13373,10 +13387,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13387,7 +13401,7 @@
         <v>76</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>75</v>
@@ -13399,7 +13413,7 @@
         <v>86</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L102" t="s" s="2">
         <v>470</v>
@@ -13407,7 +13421,9 @@
       <c r="M102" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="N102" s="2"/>
+      <c r="N102" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>75</v>
@@ -13456,19 +13472,19 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>98</v>
+        <v>327</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>75</v>
@@ -13493,7 +13509,7 @@
         <v>76</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>75</v>
@@ -13502,16 +13518,16 @@
         <v>75</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>100</v>
+        <v>473</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>101</v>
+        <v>474</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>102</v>
+        <v>475</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -13562,19 +13578,19 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>103</v>
+        <v>472</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>75</v>
@@ -13585,21 +13601,21 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>75</v>
@@ -13611,17 +13627,15 @@
         <v>75</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>75</v>
@@ -13658,31 +13672,31 @@
         <v>75</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>75</v>
@@ -13693,14 +13707,14 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>475</v>
+        <v>105</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -13713,26 +13727,24 @@
         <v>75</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K105" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>476</v>
+        <v>107</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>477</v>
+        <v>108</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="O105" t="s" s="2">
-        <v>303</v>
-      </c>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>75</v>
       </c>
@@ -13768,19 +13780,19 @@
         <v>75</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>478</v>
+        <v>113</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -13803,33 +13815,33 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>75</v>
+        <v>479</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J106" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>214</v>
+        <v>106</v>
       </c>
       <c r="L106" t="s" s="2">
         <v>480</v>
@@ -13838,10 +13850,10 @@
         <v>481</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>348</v>
+        <v>109</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>482</v>
+        <v>303</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>75</v>
@@ -13866,13 +13878,13 @@
         <v>75</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>483</v>
+        <v>75</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>484</v>
+        <v>75</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>75</v>
@@ -13890,19 +13902,19 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>75</v>
@@ -13913,10 +13925,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13924,7 +13936,7 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>85</v>
@@ -13939,19 +13951,19 @@
         <v>86</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="O107" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>75</v>
@@ -13976,13 +13988,13 @@
         <v>75</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>75</v>
+        <v>487</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>75</v>
+        <v>488</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>75</v>
@@ -14000,10 +14012,10 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>85</v>
@@ -14012,7 +14024,7 @@
         <v>97</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>326</v>
+        <v>98</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>75</v>
@@ -14023,10 +14035,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14034,7 +14046,7 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>85</v>
@@ -14046,22 +14058,22 @@
         <v>75</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="L108" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="L108" t="s" s="2">
+      <c r="M108" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>325</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>75</v>
@@ -14110,10 +14122,10 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>85</v>
@@ -14122,7 +14134,7 @@
         <v>97</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>75</v>
@@ -14133,10 +14145,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14156,22 +14168,22 @@
         <v>75</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>325</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>75</v>
@@ -14220,7 +14232,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>76</v>
@@ -14232,7 +14244,7 @@
         <v>97</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>75</v>
@@ -14243,10 +14255,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14257,7 +14269,7 @@
         <v>76</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>75</v>
@@ -14269,7 +14281,7 @@
         <v>86</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>214</v>
+        <v>500</v>
       </c>
       <c r="L110" t="s" s="2">
         <v>501</v>
@@ -14278,9 +14290,11 @@
         <v>502</v>
       </c>
       <c r="N110" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="O110" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>75</v>
       </c>
@@ -14304,13 +14318,13 @@
         <v>75</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>504</v>
+        <v>75</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>505</v>
+        <v>75</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>75</v>
@@ -14328,19 +14342,19 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>98</v>
+        <v>327</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>75</v>
@@ -14349,12 +14363,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14368,7 +14382,7 @@
         <v>77</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>75</v>
@@ -14377,16 +14391,16 @@
         <v>86</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="N111" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14412,13 +14426,13 @@
         <v>75</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>75</v>
+        <v>508</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>75</v>
+        <v>509</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>75</v>
@@ -14436,7 +14450,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -14448,7 +14462,7 @@
         <v>97</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>326</v>
+        <v>98</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>75</v>
@@ -14459,10 +14473,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14485,7 +14499,7 @@
         <v>86</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>214</v>
+        <v>511</v>
       </c>
       <c r="L112" t="s" s="2">
         <v>512</v>
@@ -14520,13 +14534,13 @@
         <v>75</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>515</v>
+        <v>75</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>516</v>
+        <v>75</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>75</v>
@@ -14544,7 +14558,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -14556,7 +14570,7 @@
         <v>97</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>98</v>
+        <v>327</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>75</v>
@@ -14565,12 +14579,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14581,27 +14595,29 @@
         <v>76</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>100</v>
+        <v>214</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>101</v>
+        <v>516</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N113" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>75</v>
@@ -14626,13 +14642,13 @@
         <v>75</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>75</v>
+        <v>519</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>75</v>
+        <v>520</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>75</v>
@@ -14650,19 +14666,19 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>103</v>
+        <v>515</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>75</v>
@@ -14673,21 +14689,21 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>75</v>
@@ -14699,17 +14715,15 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>75</v>
@@ -14746,31 +14760,31 @@
         <v>75</v>
       </c>
       <c r="AB114" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC114" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD114" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE114" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>75</v>
@@ -14781,14 +14795,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -14798,29 +14812,27 @@
         <v>77</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>226</v>
+        <v>107</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>227</v>
+        <v>108</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>75</v>
       </c>
@@ -14856,9 +14868,11 @@
         <v>75</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AC115" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="AD115" t="s" s="2">
         <v>75</v>
       </c>
@@ -14866,7 +14880,7 @@
         <v>112</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>230</v>
+        <v>113</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -14878,7 +14892,7 @@
         <v>97</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>75</v>
@@ -14887,16 +14901,14 @@
         <v>75</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="C116" t="s" s="2">
-        <v>522</v>
-      </c>
+        <v>523</v>
+      </c>
+      <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
         <v>75</v>
       </c>
@@ -14905,7 +14917,7 @@
         <v>76</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>86</v>
@@ -14920,10 +14932,10 @@
         <v>139</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>357</v>
+        <v>226</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>358</v>
+        <v>227</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>228</v>
@@ -14966,16 +14978,14 @@
         <v>75</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="AC116" s="2"/>
       <c r="AD116" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF116" t="s" s="2">
         <v>230</v>
@@ -14999,14 +15009,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="117" hidden="true">
+    <row r="117">
       <c r="A117" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B117" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="B117" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="C117" s="2"/>
+      <c r="C117" t="s" s="2">
+        <v>526</v>
+      </c>
       <c r="D117" t="s" s="2">
         <v>75</v>
       </c>
@@ -15018,25 +15030,29 @@
         <v>85</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>101</v>
+        <v>361</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>75</v>
       </c>
@@ -15084,19 +15100,19 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>75</v>
@@ -15107,21 +15123,21 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>75</v>
@@ -15133,17 +15149,15 @@
         <v>75</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>75</v>
@@ -15180,31 +15194,31 @@
         <v>75</v>
       </c>
       <c r="AB118" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC118" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD118" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE118" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>75</v>
@@ -15213,48 +15227,46 @@
         <v>75</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>237</v>
+        <v>107</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>75</v>
       </c>
@@ -15263,7 +15275,7 @@
         <v>75</v>
       </c>
       <c r="S119" t="s" s="2">
-        <v>529</v>
+        <v>75</v>
       </c>
       <c r="T119" t="s" s="2">
         <v>75</v>
@@ -15290,31 +15302,31 @@
         <v>75</v>
       </c>
       <c r="AB119" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC119" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD119" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE119" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>75</v>
@@ -15325,10 +15337,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15336,7 +15348,7 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G120" t="s" s="2">
         <v>85</v>
@@ -15351,18 +15363,20 @@
         <v>86</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O120" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P120" t="s" s="2">
         <v>75</v>
       </c>
@@ -15371,7 +15385,7 @@
         <v>75</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>75</v>
+        <v>533</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>75</v>
@@ -15410,7 +15424,7 @@
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>76</v>
@@ -15433,10 +15447,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15444,7 +15458,7 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G121" t="s" s="2">
         <v>85</v>
@@ -15459,20 +15473,18 @@
         <v>86</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>75</v>
       </c>
@@ -15520,7 +15532,7 @@
         <v>75</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>76</v>
@@ -15541,12 +15553,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="122" hidden="true">
+    <row r="122">
       <c r="A122" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15554,13 +15566,13 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G122" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>75</v>
@@ -15569,19 +15581,19 @@
         <v>86</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>75</v>
@@ -15630,7 +15642,7 @@
         <v>75</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>76</v>
@@ -15653,10 +15665,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15679,19 +15691,19 @@
         <v>86</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>267</v>
+        <v>375</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>75</v>
@@ -15740,7 +15752,7 @@
         <v>75</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>76</v>
@@ -15763,10 +15775,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15789,19 +15801,19 @@
         <v>86</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>75</v>
@@ -15850,7 +15862,7 @@
         <v>75</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
@@ -15871,12 +15883,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15890,7 +15902,7 @@
         <v>85</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>75</v>
@@ -15899,18 +15911,20 @@
         <v>86</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>214</v>
+        <v>100</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>540</v>
+        <v>272</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>541</v>
+        <v>273</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="O125" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P125" t="s" s="2">
         <v>75</v>
       </c>
@@ -15934,11 +15948,13 @@
         <v>75</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="Y125" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z125" t="s" s="2">
-        <v>543</v>
+        <v>75</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>75</v>
@@ -15956,7 +15972,7 @@
         <v>75</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>539</v>
+        <v>276</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -15974,15 +15990,15 @@
         <v>75</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>544</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="126" hidden="true">
+    <row r="126">
       <c r="A126" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15996,24 +16012,26 @@
         <v>85</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I126" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>100</v>
+        <v>214</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>101</v>
+        <v>544</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N126" s="2"/>
+        <v>545</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>546</v>
+      </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
         <v>75</v>
@@ -16038,13 +16056,11 @@
         <v>75</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="Y126" s="2"/>
       <c r="Z126" t="s" s="2">
-        <v>75</v>
+        <v>547</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>75</v>
@@ -16062,7 +16078,7 @@
         <v>75</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>103</v>
+        <v>543</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>76</v>
@@ -16071,35 +16087,35 @@
         <v>85</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>75</v>
+        <v>548</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>75</v>
@@ -16111,17 +16127,15 @@
         <v>75</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>75</v>
@@ -16158,31 +16172,31 @@
         <v>75</v>
       </c>
       <c r="AB127" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC127" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD127" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE127" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>75</v>
@@ -16193,14 +16207,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -16216,23 +16230,21 @@
         <v>75</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>548</v>
+        <v>107</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>549</v>
+        <v>108</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>75</v>
       </c>
@@ -16268,19 +16280,19 @@
         <v>75</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC128" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD128" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>230</v>
+        <v>113</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>76</v>
@@ -16292,7 +16304,7 @@
         <v>75</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>75</v>
@@ -16303,10 +16315,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16317,7 +16329,7 @@
         <v>76</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>75</v>
@@ -16326,19 +16338,23 @@
         <v>75</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>101</v>
+        <v>552</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
+        <v>553</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P129" t="s" s="2">
         <v>75</v>
       </c>
@@ -16386,19 +16402,19 @@
         <v>75</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>75</v>
@@ -16409,21 +16425,21 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>75</v>
@@ -16435,17 +16451,15 @@
         <v>75</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>75</v>
@@ -16482,31 +16496,31 @@
         <v>75</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC130" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD130" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE130" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>75</v>
@@ -16515,48 +16529,46 @@
         <v>75</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I131" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>237</v>
+        <v>107</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>75</v>
       </c>
@@ -16565,7 +16577,7 @@
         <v>75</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>553</v>
+        <v>75</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>75</v>
@@ -16592,31 +16604,31 @@
         <v>75</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC131" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD131" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE131" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>75</v>
@@ -16625,12 +16637,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="132" hidden="true">
+    <row r="132">
       <c r="A132" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -16644,7 +16656,7 @@
         <v>85</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>75</v>
@@ -16653,18 +16665,20 @@
         <v>86</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O132" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P132" t="s" s="2">
         <v>75</v>
       </c>
@@ -16673,7 +16687,7 @@
         <v>75</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>75</v>
+        <v>557</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>75</v>
@@ -16712,7 +16726,7 @@
         <v>75</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>76</v>
@@ -16733,12 +16747,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16752,7 +16766,7 @@
         <v>85</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>75</v>
@@ -16761,18 +16775,18 @@
         <v>86</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N133" s="2"/>
-      <c r="O133" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>75</v>
       </c>
@@ -16820,7 +16834,7 @@
         <v>75</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>76</v>
@@ -16841,12 +16855,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="134" hidden="true">
+    <row r="134">
       <c r="A134" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16860,7 +16874,7 @@
         <v>85</v>
       </c>
       <c r="H134" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I134" t="s" s="2">
         <v>75</v>
@@ -16869,17 +16883,17 @@
         <v>86</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>75</v>
@@ -16928,7 +16942,7 @@
         <v>75</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>76</v>
@@ -16951,10 +16965,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16977,19 +16991,17 @@
         <v>86</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N135" s="2"/>
       <c r="O135" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>75</v>
@@ -17038,7 +17050,7 @@
         <v>75</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>76</v>
@@ -17061,10 +17073,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17087,19 +17099,19 @@
         <v>86</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>75</v>
@@ -17148,7 +17160,7 @@
         <v>75</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>76</v>
@@ -17171,10 +17183,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17185,7 +17197,7 @@
         <v>76</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>75</v>
@@ -17194,21 +17206,23 @@
         <v>75</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>560</v>
+        <v>100</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>561</v>
+        <v>272</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>562</v>
+        <v>273</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="O137" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="O137" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P137" t="s" s="2">
         <v>75</v>
       </c>
@@ -17256,19 +17270,19 @@
         <v>75</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>559</v>
+        <v>276</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI137" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>326</v>
+        <v>98</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>75</v>
@@ -17279,10 +17293,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17296,7 +17310,7 @@
         <v>77</v>
       </c>
       <c r="H138" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I138" t="s" s="2">
         <v>75</v>
@@ -17305,7 +17319,7 @@
         <v>75</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>214</v>
+        <v>564</v>
       </c>
       <c r="L138" t="s" s="2">
         <v>565</v>
@@ -17340,29 +17354,31 @@
         <v>75</v>
       </c>
       <c r="X138" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>568</v>
+        <v>75</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>569</v>
+        <v>75</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AC138" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD138" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>76</v>
@@ -17374,25 +17390,23 @@
         <v>97</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>98</v>
+        <v>327</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>570</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C139" t="s" s="2">
-        <v>572</v>
-      </c>
+        <v>568</v>
+      </c>
+      <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
         <v>75</v>
       </c>
@@ -17416,13 +17430,13 @@
         <v>214</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -17448,9 +17462,11 @@
         <v>75</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="Y139" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>572</v>
+      </c>
       <c r="Z139" t="s" s="2">
         <v>573</v>
       </c>
@@ -17458,19 +17474,17 @@
         <v>75</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="AC139" s="2"/>
       <c r="AD139" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE139" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>76</v>
@@ -17488,17 +17502,19 @@
         <v>75</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>75</v>
+        <v>574</v>
       </c>
     </row>
-    <row r="140" hidden="true">
+    <row r="140">
       <c r="A140" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="C140" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="C140" t="s" s="2">
+        <v>576</v>
+      </c>
       <c r="D140" t="s" s="2">
         <v>75</v>
       </c>
@@ -17507,10 +17523,10 @@
         <v>76</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H140" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I140" t="s" s="2">
         <v>75</v>
@@ -17519,15 +17535,17 @@
         <v>75</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>100</v>
+        <v>214</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>101</v>
+        <v>569</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N140" s="2"/>
+        <v>570</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>571</v>
+      </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>75</v>
@@ -17552,13 +17570,11 @@
         <v>75</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y140" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="Y140" s="2"/>
       <c r="Z140" t="s" s="2">
-        <v>75</v>
+        <v>577</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>75</v>
@@ -17576,19 +17592,19 @@
         <v>75</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>103</v>
+        <v>568</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>75</v>
@@ -17599,21 +17615,21 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>75</v>
@@ -17625,17 +17641,15 @@
         <v>75</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N141" s="2"/>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>75</v>
@@ -17672,31 +17686,31 @@
         <v>75</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC141" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD141" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE141" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>75</v>
@@ -17707,14 +17721,14 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -17730,23 +17744,21 @@
         <v>75</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>580</v>
+        <v>107</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>581</v>
+        <v>108</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>75</v>
       </c>
@@ -17782,19 +17794,19 @@
         <v>75</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC142" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD142" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>230</v>
+        <v>113</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>76</v>
@@ -17806,7 +17818,7 @@
         <v>75</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>75</v>
@@ -17831,7 +17843,7 @@
         <v>76</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>75</v>
@@ -17840,19 +17852,23 @@
         <v>75</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>101</v>
+        <v>584</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N143" s="2"/>
-      <c r="O143" s="2"/>
+        <v>585</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O143" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P143" t="s" s="2">
         <v>75</v>
       </c>
@@ -17900,19 +17916,19 @@
         <v>75</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK143" t="s" s="2">
         <v>75</v>
@@ -17923,21 +17939,21 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>75</v>
@@ -17949,17 +17965,15 @@
         <v>75</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N144" s="2"/>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
         <v>75</v>
@@ -17996,31 +18010,31 @@
         <v>75</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC144" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD144" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE144" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK144" t="s" s="2">
         <v>75</v>
@@ -18031,21 +18045,21 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>75</v>
@@ -18054,23 +18068,21 @@
         <v>75</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>237</v>
+        <v>107</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O145" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
         <v>75</v>
       </c>
@@ -18079,7 +18091,7 @@
         <v>75</v>
       </c>
       <c r="S145" t="s" s="2">
-        <v>588</v>
+        <v>75</v>
       </c>
       <c r="T145" t="s" s="2">
         <v>75</v>
@@ -18106,31 +18118,31 @@
         <v>75</v>
       </c>
       <c r="AB145" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC145" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD145" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE145" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>75</v>
@@ -18141,10 +18153,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18167,18 +18179,20 @@
         <v>86</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O146" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O146" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P146" t="s" s="2">
         <v>75</v>
       </c>
@@ -18187,7 +18201,7 @@
         <v>75</v>
       </c>
       <c r="S146" t="s" s="2">
-        <v>75</v>
+        <v>592</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>75</v>
@@ -18226,7 +18240,7 @@
         <v>75</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>76</v>
@@ -18247,12 +18261,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -18260,13 +18274,13 @@
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G147" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I147" t="s" s="2">
         <v>75</v>
@@ -18275,18 +18289,18 @@
         <v>86</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N147" s="2"/>
-      <c r="O147" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>75</v>
       </c>
@@ -18334,7 +18348,7 @@
         <v>75</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>76</v>
@@ -18355,12 +18369,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="148" hidden="true">
+    <row r="148">
       <c r="A148" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -18368,13 +18382,13 @@
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G148" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H148" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I148" t="s" s="2">
         <v>75</v>
@@ -18383,17 +18397,17 @@
         <v>86</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>75</v>
@@ -18442,7 +18456,7 @@
         <v>75</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>76</v>
@@ -18465,10 +18479,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18491,19 +18505,17 @@
         <v>86</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N149" s="2"/>
       <c r="O149" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>75</v>
@@ -18552,7 +18564,7 @@
         <v>75</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>76</v>
@@ -18575,10 +18587,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -18601,19 +18613,19 @@
         <v>86</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>75</v>
@@ -18662,7 +18674,7 @@
         <v>75</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>76</v>
@@ -18683,16 +18695,14 @@
         <v>75</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C151" t="s" s="2">
-        <v>600</v>
-      </c>
+        <v>602</v>
+      </c>
+      <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
         <v>75</v>
       </c>
@@ -18701,30 +18711,32 @@
         <v>76</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H151" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I151" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J151" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I151" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J151" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="K151" t="s" s="2">
-        <v>214</v>
+        <v>100</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>565</v>
+        <v>272</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>566</v>
+        <v>273</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="O151" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="O151" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P151" t="s" s="2">
         <v>75</v>
       </c>
@@ -18748,11 +18760,13 @@
         <v>75</v>
       </c>
       <c r="X151" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="Y151" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y151" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z151" t="s" s="2">
-        <v>601</v>
+        <v>75</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>75</v>
@@ -18770,16 +18784,16 @@
         <v>75</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>564</v>
+        <v>276</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ151" t="s" s="2">
         <v>98</v>
@@ -18791,14 +18805,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="152" hidden="true">
+    <row r="152">
       <c r="A152" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="C152" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="C152" t="s" s="2">
+        <v>604</v>
+      </c>
       <c r="D152" t="s" s="2">
         <v>75</v>
       </c>
@@ -18807,10 +18823,10 @@
         <v>76</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H152" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I152" t="s" s="2">
         <v>75</v>
@@ -18819,15 +18835,17 @@
         <v>75</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>100</v>
+        <v>214</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>101</v>
+        <v>569</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N152" s="2"/>
+        <v>570</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>571</v>
+      </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
         <v>75</v>
@@ -18852,13 +18870,11 @@
         <v>75</v>
       </c>
       <c r="X152" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y152" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="Y152" s="2"/>
       <c r="Z152" t="s" s="2">
-        <v>75</v>
+        <v>605</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>75</v>
@@ -18876,19 +18892,19 @@
         <v>75</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>103</v>
+        <v>568</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK152" t="s" s="2">
         <v>75</v>
@@ -18899,21 +18915,21 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>75</v>
@@ -18925,17 +18941,15 @@
         <v>75</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N153" s="2"/>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>75</v>
@@ -18972,31 +18986,31 @@
         <v>75</v>
       </c>
       <c r="AB153" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC153" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD153" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE153" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>75</v>
@@ -19007,14 +19021,14 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
@@ -19030,23 +19044,21 @@
         <v>75</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>605</v>
+        <v>107</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>606</v>
+        <v>108</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>75</v>
       </c>
@@ -19082,19 +19094,19 @@
         <v>75</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>230</v>
+        <v>113</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>76</v>
@@ -19106,7 +19118,7 @@
         <v>75</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>75</v>
@@ -19117,7 +19129,7 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>583</v>
@@ -19131,7 +19143,7 @@
         <v>76</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>75</v>
@@ -19140,19 +19152,23 @@
         <v>75</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>101</v>
+        <v>609</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N155" s="2"/>
-      <c r="O155" s="2"/>
+        <v>610</v>
+      </c>
+      <c r="N155" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O155" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P155" t="s" s="2">
         <v>75</v>
       </c>
@@ -19200,19 +19216,19 @@
         <v>75</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI155" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK155" t="s" s="2">
         <v>75</v>
@@ -19223,21 +19239,21 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>75</v>
@@ -19249,17 +19265,15 @@
         <v>75</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N156" s="2"/>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
         <v>75</v>
@@ -19296,31 +19310,31 @@
         <v>75</v>
       </c>
       <c r="AB156" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC156" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD156" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE156" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>75</v>
@@ -19331,21 +19345,21 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>75</v>
@@ -19354,23 +19368,21 @@
         <v>75</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>237</v>
+        <v>107</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>75</v>
       </c>
@@ -19379,7 +19391,7 @@
         <v>75</v>
       </c>
       <c r="S157" t="s" s="2">
-        <v>610</v>
+        <v>75</v>
       </c>
       <c r="T157" t="s" s="2">
         <v>75</v>
@@ -19406,31 +19418,31 @@
         <v>75</v>
       </c>
       <c r="AB157" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC157" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD157" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE157" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>75</v>
@@ -19441,10 +19453,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -19452,7 +19464,7 @@
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G158" t="s" s="2">
         <v>85</v>
@@ -19467,18 +19479,20 @@
         <v>86</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O158" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O158" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P158" t="s" s="2">
         <v>75</v>
       </c>
@@ -19487,7 +19501,7 @@
         <v>75</v>
       </c>
       <c r="S158" t="s" s="2">
-        <v>75</v>
+        <v>614</v>
       </c>
       <c r="T158" t="s" s="2">
         <v>75</v>
@@ -19526,7 +19540,7 @@
         <v>75</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>76</v>
@@ -19549,10 +19563,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -19560,7 +19574,7 @@
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G159" t="s" s="2">
         <v>85</v>
@@ -19575,18 +19589,18 @@
         <v>86</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N159" s="2"/>
-      <c r="O159" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N159" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
         <v>75</v>
       </c>
@@ -19634,7 +19648,7 @@
         <v>75</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>76</v>
@@ -19657,10 +19671,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -19668,7 +19682,7 @@
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G160" t="s" s="2">
         <v>85</v>
@@ -19683,17 +19697,17 @@
         <v>86</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>75</v>
@@ -19742,7 +19756,7 @@
         <v>75</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>76</v>
@@ -19765,10 +19779,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -19791,19 +19805,17 @@
         <v>86</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>75</v>
@@ -19852,7 +19864,7 @@
         <v>75</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>76</v>
@@ -19875,10 +19887,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -19901,19 +19913,19 @@
         <v>86</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>75</v>
@@ -19962,7 +19974,7 @@
         <v>75</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>76</v>
@@ -19985,10 +19997,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>616</v>
+        <v>602</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -19999,7 +20011,7 @@
         <v>76</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>75</v>
@@ -20008,22 +20020,22 @@
         <v>75</v>
       </c>
       <c r="J163" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>617</v>
+        <v>100</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>618</v>
+        <v>272</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>619</v>
+        <v>273</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>325</v>
+        <v>274</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>620</v>
+        <v>275</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>75</v>
@@ -20072,19 +20084,19 @@
         <v>75</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>616</v>
+        <v>276</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH163" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>326</v>
+        <v>98</v>
       </c>
       <c r="AK163" t="s" s="2">
         <v>75</v>
@@ -20095,10 +20107,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -20121,7 +20133,7 @@
         <v>75</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>214</v>
+        <v>621</v>
       </c>
       <c r="L164" t="s" s="2">
         <v>622</v>
@@ -20130,9 +20142,11 @@
         <v>623</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O164" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>624</v>
+      </c>
       <c r="P164" t="s" s="2">
         <v>75</v>
       </c>
@@ -20156,13 +20170,13 @@
         <v>75</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>624</v>
+        <v>75</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>625</v>
+        <v>75</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>75</v>
@@ -20180,7 +20194,7 @@
         <v>75</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>76</v>
@@ -20192,7 +20206,7 @@
         <v>97</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>98</v>
+        <v>327</v>
       </c>
       <c r="AK164" t="s" s="2">
         <v>75</v>
@@ -20201,12 +20215,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -20220,7 +20234,7 @@
         <v>77</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>75</v>
@@ -20229,16 +20243,16 @@
         <v>75</v>
       </c>
       <c r="K165" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L165" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M165" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="L165" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="M165" t="s" s="2">
-        <v>629</v>
-      </c>
       <c r="N165" t="s" s="2">
-        <v>630</v>
+        <v>352</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -20264,13 +20278,13 @@
         <v>75</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>75</v>
+        <v>628</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>75</v>
+        <v>629</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>75</v>
@@ -20288,7 +20302,7 @@
         <v>75</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>76</v>
@@ -20309,12 +20323,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="166" hidden="true">
+    <row r="166">
       <c r="A166" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -20328,7 +20342,7 @@
         <v>77</v>
       </c>
       <c r="H166" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I166" t="s" s="2">
         <v>75</v>
@@ -20337,7 +20351,7 @@
         <v>75</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>469</v>
+        <v>631</v>
       </c>
       <c r="L166" t="s" s="2">
         <v>632</v>
@@ -20345,7 +20359,9 @@
       <c r="M166" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="N166" s="2"/>
+      <c r="N166" t="s" s="2">
+        <v>634</v>
+      </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
         <v>75</v>
@@ -20394,7 +20410,7 @@
         <v>75</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>76</v>
@@ -20417,10 +20433,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -20431,7 +20447,7 @@
         <v>76</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H167" t="s" s="2">
         <v>75</v>
@@ -20443,13 +20459,13 @@
         <v>75</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>100</v>
+        <v>473</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>101</v>
+        <v>636</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>102</v>
+        <v>637</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -20500,19 +20516,19 @@
         <v>75</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>103</v>
+        <v>635</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH167" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>75</v>
@@ -20523,21 +20539,21 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>75</v>
@@ -20549,17 +20565,15 @@
         <v>75</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N168" s="2"/>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>75</v>
@@ -20596,31 +20610,31 @@
         <v>75</v>
       </c>
       <c r="AB168" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC168" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD168" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE168" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK168" t="s" s="2">
         <v>75</v>
@@ -20631,14 +20645,14 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>475</v>
+        <v>105</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
@@ -20651,26 +20665,24 @@
         <v>75</v>
       </c>
       <c r="I169" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J169" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K169" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>476</v>
+        <v>107</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>477</v>
+        <v>108</v>
       </c>
       <c r="N169" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="O169" t="s" s="2">
-        <v>303</v>
-      </c>
+      <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
         <v>75</v>
       </c>
@@ -20706,19 +20718,19 @@
         <v>75</v>
       </c>
       <c r="AB169" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC169" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD169" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE169" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>478</v>
+        <v>113</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>76</v>
@@ -20741,44 +20753,46 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>75</v>
+        <v>479</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G170" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H170" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I170" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J170" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>214</v>
+        <v>106</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>638</v>
+        <v>480</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>639</v>
+        <v>481</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O170" s="2"/>
+        <v>109</v>
+      </c>
+      <c r="O170" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="P170" t="s" s="2">
         <v>75</v>
       </c>
@@ -20802,13 +20816,13 @@
         <v>75</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>640</v>
+        <v>75</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>641</v>
+        <v>75</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>75</v>
@@ -20826,19 +20840,19 @@
         <v>75</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>637</v>
+        <v>482</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH170" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI170" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK170" t="s" s="2">
         <v>75</v>
@@ -20849,10 +20863,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -20860,7 +20874,7 @@
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G171" t="s" s="2">
         <v>85</v>
@@ -20875,16 +20889,16 @@
         <v>75</v>
       </c>
       <c r="K171" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L171" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="M171" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="L171" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="M171" t="s" s="2">
-        <v>645</v>
-      </c>
       <c r="N171" t="s" s="2">
-        <v>325</v>
+        <v>352</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -20910,13 +20924,13 @@
         <v>75</v>
       </c>
       <c r="X171" t="s" s="2">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>75</v>
+        <v>644</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>75</v>
+        <v>645</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>75</v>
@@ -20934,10 +20948,10 @@
         <v>75</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AG171" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH171" t="s" s="2">
         <v>85</v>
@@ -20946,7 +20960,7 @@
         <v>97</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>326</v>
+        <v>98</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>75</v>
@@ -20968,10 +20982,10 @@
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>75</v>
@@ -20992,11 +21006,9 @@
         <v>649</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="O172" t="s" s="2">
-        <v>651</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>75</v>
       </c>
@@ -21047,16 +21059,16 @@
         <v>646</v>
       </c>
       <c r="AG172" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH172" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI172" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AK172" t="s" s="2">
         <v>75</v>
@@ -21065,12 +21077,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -21084,7 +21096,7 @@
         <v>77</v>
       </c>
       <c r="H173" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I173" t="s" s="2">
         <v>75</v>
@@ -21093,18 +21105,20 @@
         <v>75</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>214</v>
+        <v>651</v>
       </c>
       <c r="L173" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="M173" t="s" s="2">
         <v>653</v>
       </c>
-      <c r="M173" t="s" s="2">
+      <c r="N173" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="N173" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="O173" s="2"/>
+      <c r="O173" t="s" s="2">
+        <v>655</v>
+      </c>
       <c r="P173" t="s" s="2">
         <v>75</v>
       </c>
@@ -21128,13 +21142,13 @@
         <v>75</v>
       </c>
       <c r="X173" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>655</v>
+        <v>75</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>656</v>
+        <v>75</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>75</v>
@@ -21152,7 +21166,7 @@
         <v>75</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>76</v>
@@ -21164,7 +21178,7 @@
         <v>97</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>98</v>
+        <v>327</v>
       </c>
       <c r="AK173" t="s" s="2">
         <v>75</v>
@@ -21173,12 +21187,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="174" hidden="true">
+    <row r="174">
       <c r="A174" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -21189,10 +21203,10 @@
         <v>76</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H174" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I174" t="s" s="2">
         <v>75</v>
@@ -21201,15 +21215,17 @@
         <v>75</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>100</v>
+        <v>214</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>101</v>
+        <v>657</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N174" s="2"/>
+        <v>658</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>654</v>
+      </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
         <v>75</v>
@@ -21234,13 +21250,13 @@
         <v>75</v>
       </c>
       <c r="X174" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Y174" t="s" s="2">
-        <v>75</v>
+        <v>659</v>
       </c>
       <c r="Z174" t="s" s="2">
-        <v>75</v>
+        <v>660</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>75</v>
@@ -21258,19 +21274,19 @@
         <v>75</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>103</v>
+        <v>656</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH174" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>75</v>
@@ -21281,21 +21297,21 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G175" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H175" t="s" s="2">
         <v>75</v>
@@ -21307,17 +21323,15 @@
         <v>75</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N175" s="2"/>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
         <v>75</v>
@@ -21354,31 +21368,31 @@
         <v>75</v>
       </c>
       <c r="AB175" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC175" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD175" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE175" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH175" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI175" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK175" t="s" s="2">
         <v>75</v>
@@ -21389,14 +21403,14 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -21406,29 +21420,27 @@
         <v>77</v>
       </c>
       <c r="H176" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I176" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J176" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>226</v>
+        <v>107</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>227</v>
+        <v>108</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O176" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
         <v>75</v>
       </c>
@@ -21464,10 +21476,10 @@
         <v>75</v>
       </c>
       <c r="AB176" t="s" s="2">
-        <v>660</v>
+        <v>110</v>
       </c>
       <c r="AC176" t="s" s="2">
-        <v>661</v>
+        <v>111</v>
       </c>
       <c r="AD176" t="s" s="2">
         <v>75</v>
@@ -21476,7 +21488,7 @@
         <v>112</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>230</v>
+        <v>113</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>76</v>
@@ -21488,7 +21500,7 @@
         <v>75</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>75</v>
@@ -21499,10 +21511,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -21513,10 +21525,10 @@
         <v>76</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H177" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I177" t="s" s="2">
         <v>75</v>
@@ -21525,19 +21537,19 @@
         <v>86</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>272</v>
+        <v>226</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>273</v>
+        <v>227</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>274</v>
+        <v>228</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>275</v>
+        <v>229</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>75</v>
@@ -21574,25 +21586,25 @@
         <v>75</v>
       </c>
       <c r="AB177" t="s" s="2">
-        <v>75</v>
+        <v>664</v>
       </c>
       <c r="AC177" t="s" s="2">
-        <v>75</v>
+        <v>665</v>
       </c>
       <c r="AD177" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE177" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>276</v>
+        <v>230</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH177" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI177" t="s" s="2">
         <v>75</v>
@@ -21607,8 +21619,118 @@
         <v>75</v>
       </c>
     </row>
+    <row r="178" hidden="true">
+      <c r="A178" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B178" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="C178" s="2"/>
+      <c r="D178" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E178" s="2"/>
+      <c r="F178" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G178" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H178" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I178" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J178" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K178" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L178" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M178" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N178" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="O178" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="P178" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q178" s="2"/>
+      <c r="R178" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S178" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T178" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U178" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V178" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W178" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X178" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y178" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z178" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA178" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB178" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC178" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD178" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE178" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF178" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AG178" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH178" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI178" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ178" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK178" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL178" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AL177">
+  <autoFilter ref="A1:AL178">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -21618,7 +21740,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI176">
+  <conditionalFormatting sqref="A2:AI177">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:40:52+00:00</t>
+    <t>2026-08-28T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:03:44+00:00</t>
+    <t>2026-08-28T09:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:05:47+00:00</t>
+    <t>2026-08-28T09:25:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:25:31+00:00</t>
+    <t>2026-08-28T09:53:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:53:30+00:00</t>
+    <t>2026-08-28T10:16:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:16:47+00:00</t>
+    <t>2026-08-28T12:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:10:16+00:00</t>
+    <t>2026-08-28T12:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:26:30+00:00</t>
+    <t>2026-08-28T12:47:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6118" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6117" uniqueCount="667">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:47:27+00:00</t>
+    <t>2026-08-28T13:10:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1287,10 +1287,10 @@
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
+    <t>Seitenlokalisation (OPS-Seitenzusatz R/L/B)</t>
+  </si>
+  <si>
+    <t>Seitenangabe bei paarigen Organen und OPS-Codes mit Seitenzusatzpflicht über die Basisprofil-Extension seitenlokalisation (R/L/B). Das oBDS sieht am OP kein eigenes Seitenfeld vor; führend ist der OPS-Seitenzusatz.</t>
   </si>
   <si>
     <t>Procedure.code.coding:ops.system</t>
@@ -11106,7 +11106,7 @@
         <v>405</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11133,9 +11133,7 @@
       <c r="M81" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="N81" t="s" s="2">
-        <v>109</v>
-      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>75</v>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:10:09+00:00</t>
+    <t>2026-08-28T13:33:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:33:24+00:00</t>
+    <t>2026-08-28T13:57:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:33:40+00:00</t>
+    <t>2026-08-28T14:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:57:41+00:00</t>
+    <t>2026-08-28T15:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:24:04+00:00</t>
+    <t>2026-08-28T15:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:48:09+00:00</t>
+    <t>2026-08-28T18:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T18:25:22+00:00</t>
+    <t>2026-08-28T19:18:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T19:18:26+00:00</t>
+    <t>2026-08-31T13:44:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:44:47+00:00</t>
+    <t>2026-08-31T14:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:28:40+00:00</t>
+    <t>2026-08-31T15:22:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:22:09+00:00</t>
+    <t>2026-09-01T08:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:53:35+00:00</t>
+    <t>2026-09-01T09:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:38:31+00:00</t>
+    <t>2026-09-01T11:08:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:08:21+00:00</t>
+    <t>2026-09-01T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:29:01+00:00</t>
+    <t>2026-09-01T19:43:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$217</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8020" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8061" uniqueCount="793">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T19:43:49+00:00</t>
+    <t>2026-09-01T20:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1483,6 +1483,9 @@
   </si>
   <si>
     <t>Procedure.code.coding.extension.value[x].code</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Procedure.code.coding:ops.extension:Seitenlokalisation.value[x].display</t>
@@ -2014,6 +2017,22 @@
   </si>
   <si>
     <t>Procedure.bodySite.extension</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension:bodySite</t>
+  </si>
+  <si>
+    <t>bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {bodySite}
+</t>
+  </si>
+  <si>
+    <t>Target anatomic location or structure</t>
+  </si>
+  <si>
+    <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
   </si>
   <si>
     <t>Procedure.bodySite.coding</t>
@@ -2769,7 +2788,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO216"/>
+  <dimension ref="A1:AO217"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.5703125" customWidth="true" bestFit="true"/>
@@ -5129,7 +5148,7 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>117</v>
@@ -5361,7 +5380,7 @@
         <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>101</v>
@@ -13886,7 +13905,7 @@
         <v>80</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>117</v>
@@ -14235,7 +14254,7 @@
         <v>80</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>117</v>
@@ -14465,7 +14484,7 @@
         <v>89</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>101</v>
@@ -14697,7 +14716,7 @@
         <v>80</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>117</v>
@@ -14816,7 +14835,7 @@
         <v>89</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>101</v>
@@ -14933,7 +14952,7 @@
         <v>89</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>101</v>
@@ -14990,7 +15009,9 @@
       <c r="M105" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="N105" s="2"/>
+      <c r="N105" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="O105" t="s" s="2">
         <v>248</v>
       </c>
@@ -15050,7 +15071,7 @@
         <v>89</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>101</v>
@@ -15073,10 +15094,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15107,7 +15128,9 @@
       <c r="M106" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="N106" s="2"/>
+      <c r="N106" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="O106" t="s" s="2">
         <v>255</v>
       </c>
@@ -15167,7 +15190,7 @@
         <v>89</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>101</v>
@@ -15190,10 +15213,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15286,7 +15309,7 @@
         <v>89</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>101</v>
@@ -15309,10 +15332,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15338,7 +15361,7 @@
         <v>130</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M108" t="s" s="2">
         <v>231</v>
@@ -15354,7 +15377,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>78</v>
@@ -15405,7 +15428,7 @@
         <v>89</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>101</v>
@@ -15428,10 +15451,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15457,10 +15480,10 @@
         <v>103</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>241</v>
@@ -15522,7 +15545,7 @@
         <v>89</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>101</v>
@@ -15531,7 +15554,7 @@
         <v>78</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
@@ -15545,10 +15568,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15574,12 +15597,14 @@
         <v>164</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M110" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="N110" s="2"/>
+      <c r="N110" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="O110" t="s" s="2">
         <v>248</v>
       </c>
@@ -15594,7 +15619,7 @@
         <v>78</v>
       </c>
       <c r="T110" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="U110" t="s" s="2">
         <v>78</v>
@@ -15639,16 +15664,16 @@
         <v>89</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
@@ -15662,10 +15687,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15696,7 +15721,9 @@
       <c r="M111" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="N111" s="2"/>
+      <c r="N111" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="O111" t="s" s="2">
         <v>255</v>
       </c>
@@ -15756,7 +15783,7 @@
         <v>89</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>101</v>
@@ -15779,10 +15806,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15875,7 +15902,7 @@
         <v>89</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>101</v>
@@ -15898,7 +15925,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>436</v>
@@ -15967,7 +15994,7 @@
       </c>
       <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>78</v>
@@ -16017,7 +16044,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>445</v>
@@ -16132,7 +16159,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>447</v>
@@ -16249,10 +16276,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16368,10 +16395,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16485,10 +16512,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16602,10 +16629,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16719,10 +16746,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16838,10 +16865,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16957,14 +16984,14 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -16983,13 +17010,13 @@
         <v>90</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17040,7 +17067,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>89</v>
@@ -17061,21 +17088,21 @@
         <v>78</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17187,10 +17214,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17304,10 +17331,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17333,13 +17360,13 @@
         <v>103</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -17389,7 +17416,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17398,7 +17425,7 @@
         <v>89</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AJ125" t="s" s="2">
         <v>101</v>
@@ -17421,10 +17448,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17450,13 +17477,13 @@
         <v>130</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -17485,10 +17512,10 @@
         <v>146</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>78</v>
@@ -17506,7 +17533,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17538,10 +17565,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17567,13 +17594,13 @@
         <v>342</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17623,7 +17650,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17655,10 +17682,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17684,13 +17711,13 @@
         <v>103</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -17740,7 +17767,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17772,10 +17799,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17798,16 +17825,16 @@
         <v>90</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -17857,7 +17884,7 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17878,21 +17905,21 @@
         <v>78</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18004,10 +18031,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18121,10 +18148,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18150,13 +18177,13 @@
         <v>103</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18206,7 +18233,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -18215,7 +18242,7 @@
         <v>89</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>101</v>
@@ -18238,10 +18265,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18267,13 +18294,13 @@
         <v>130</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -18302,10 +18329,10 @@
         <v>146</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>78</v>
@@ -18323,7 +18350,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18355,10 +18382,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18384,13 +18411,13 @@
         <v>342</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -18440,7 +18467,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18472,10 +18499,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18501,13 +18528,13 @@
         <v>103</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -18557,7 +18584,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18589,10 +18616,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18618,13 +18645,13 @@
         <v>208</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -18662,17 +18689,17 @@
         <v>78</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AC136" s="2"/>
       <c r="AD136" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE136" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18693,24 +18720,24 @@
         <v>78</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AO136" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>78</v>
@@ -18735,13 +18762,13 @@
         <v>208</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -18791,7 +18818,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -18809,27 +18836,27 @@
         <v>78</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>78</v>
@@ -18851,16 +18878,16 @@
         <v>90</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -18910,7 +18937,7 @@
         <v>78</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -18931,21 +18958,21 @@
         <v>78</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18968,13 +18995,13 @@
         <v>90</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19025,7 +19052,7 @@
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -19049,7 +19076,7 @@
         <v>78</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>78</v>
@@ -19057,10 +19084,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19083,13 +19110,13 @@
         <v>90</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -19140,7 +19167,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -19164,7 +19191,7 @@
         <v>78</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>78</v>
@@ -19172,10 +19199,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19198,13 +19225,13 @@
         <v>90</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -19255,7 +19282,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19276,7 +19303,7 @@
         <v>78</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>78</v>
@@ -19287,10 +19314,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19402,10 +19429,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19519,14 +19546,14 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -19548,10 +19575,10 @@
         <v>109</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>112</v>
@@ -19606,7 +19633,7 @@
         <v>78</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -19638,10 +19665,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19667,14 +19694,14 @@
         <v>277</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>78</v>
@@ -19702,10 +19729,10 @@
         <v>154</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>78</v>
@@ -19723,7 +19750,7 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -19744,21 +19771,21 @@
         <v>78</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO145" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19781,17 +19808,17 @@
         <v>90</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>78</v>
@@ -19840,7 +19867,7 @@
         <v>78</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>89</v>
@@ -19861,21 +19888,21 @@
         <v>78</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19898,17 +19925,17 @@
         <v>78</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>78</v>
@@ -19957,7 +19984,7 @@
         <v>78</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -19989,10 +20016,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20015,17 +20042,17 @@
         <v>90</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>78</v>
@@ -20074,7 +20101,7 @@
         <v>78</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20098,7 +20125,7 @@
         <v>78</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>78</v>
@@ -20106,10 +20133,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20135,13 +20162,13 @@
         <v>277</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -20170,10 +20197,10 @@
         <v>154</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>78</v>
@@ -20191,7 +20218,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20212,10 +20239,10 @@
         <v>78</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>78</v>
@@ -20223,10 +20250,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20249,16 +20276,16 @@
         <v>90</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -20308,7 +20335,7 @@
         <v>78</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
@@ -20329,10 +20356,10 @@
         <v>78</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>78</v>
@@ -20340,10 +20367,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20369,13 +20396,13 @@
         <v>277</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20404,10 +20431,10 @@
         <v>154</v>
       </c>
       <c r="Y151" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="Z151" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>78</v>
@@ -20425,7 +20452,7 @@
         <v>78</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
@@ -20452,15 +20479,15 @@
         <v>78</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20572,10 +20599,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20689,12 +20716,14 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="C154" s="2"/>
+      <c r="C154" t="s" s="2">
+        <v>645</v>
+      </c>
       <c r="D154" t="s" s="2">
         <v>78</v>
       </c>
@@ -20703,32 +20732,28 @@
         <v>79</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H154" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I154" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>142</v>
+        <v>646</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>283</v>
+        <v>647</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>648</v>
+      </c>
+      <c r="N154" s="2"/>
+      <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>78</v>
       </c>
@@ -20764,17 +20789,19 @@
         <v>78</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AC154" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC154" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD154" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>287</v>
+        <v>116</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -20786,7 +20813,7 @@
         <v>78</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>78</v>
@@ -20801,19 +20828,17 @@
         <v>78</v>
       </c>
       <c r="AO154" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="C155" t="s" s="2">
-        <v>646</v>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
         <v>78</v>
       </c>
@@ -20822,7 +20847,7 @@
         <v>79</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>90</v>
@@ -20837,10 +20862,10 @@
         <v>142</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>404</v>
+        <v>283</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>405</v>
+        <v>284</v>
       </c>
       <c r="N155" t="s" s="2">
         <v>285</v>
@@ -20883,16 +20908,14 @@
         <v>78</v>
       </c>
       <c r="AB155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC155" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>650</v>
+      </c>
+      <c r="AC155" s="2"/>
       <c r="AD155" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE155" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF155" t="s" s="2">
         <v>287</v>
@@ -20925,14 +20948,16 @@
         <v>288</v>
       </c>
     </row>
-    <row r="156" hidden="true">
+    <row r="156">
       <c r="A156" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="C156" s="2"/>
+        <v>649</v>
+      </c>
+      <c r="C156" t="s" s="2">
+        <v>652</v>
+      </c>
       <c r="D156" t="s" s="2">
         <v>78</v>
       </c>
@@ -20944,25 +20969,29 @@
         <v>89</v>
       </c>
       <c r="H156" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I156" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>104</v>
+        <v>404</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N156" s="2"/>
-      <c r="O156" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="N156" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O156" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P156" t="s" s="2">
         <v>78</v>
       </c>
@@ -21010,19 +21039,19 @@
         <v>78</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>106</v>
+        <v>287</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>78</v>
@@ -21037,26 +21066,26 @@
         <v>78</v>
       </c>
       <c r="AO156" t="s" s="2">
-        <v>78</v>
+        <v>288</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>78</v>
@@ -21068,17 +21097,15 @@
         <v>78</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N157" s="2"/>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>78</v>
@@ -21115,31 +21142,31 @@
         <v>78</v>
       </c>
       <c r="AB157" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC157" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD157" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE157" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>78</v>
@@ -21157,48 +21184,46 @@
         <v>78</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H158" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I158" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J158" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O158" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
         <v>78</v>
       </c>
@@ -21207,7 +21232,7 @@
         <v>78</v>
       </c>
       <c r="S158" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="T158" t="s" s="2">
         <v>78</v>
@@ -21234,31 +21259,31 @@
         <v>78</v>
       </c>
       <c r="AB158" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC158" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD158" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE158" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>235</v>
+        <v>116</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH158" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI158" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK158" t="s" s="2">
         <v>78</v>
@@ -21273,15 +21298,15 @@
         <v>78</v>
       </c>
       <c r="AO158" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21289,7 +21314,7 @@
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G159" t="s" s="2">
         <v>89</v>
@@ -21304,18 +21329,20 @@
         <v>90</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O159" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="O159" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P159" t="s" s="2">
         <v>78</v>
       </c>
@@ -21324,7 +21351,7 @@
         <v>78</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="T159" t="s" s="2">
         <v>78</v>
@@ -21363,7 +21390,7 @@
         <v>78</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21390,15 +21417,15 @@
         <v>78</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21406,7 +21433,7 @@
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G160" t="s" s="2">
         <v>89</v>
@@ -21421,18 +21448,18 @@
         <v>90</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N160" s="2"/>
-      <c r="O160" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>78</v>
       </c>
@@ -21480,7 +21507,7 @@
         <v>78</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -21507,15 +21534,15 @@
         <v>78</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
-    <row r="161" hidden="true">
+    <row r="161">
       <c r="A161" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21523,13 +21550,13 @@
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G161" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H161" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I161" t="s" s="2">
         <v>78</v>
@@ -21538,17 +21565,17 @@
         <v>90</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>78</v>
@@ -21597,7 +21624,7 @@
         <v>78</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -21624,15 +21651,15 @@
         <v>78</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21655,19 +21682,17 @@
         <v>90</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>260</v>
+        <v>103</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>78</v>
@@ -21716,7 +21741,7 @@
         <v>78</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -21743,15 +21768,15 @@
         <v>78</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21774,19 +21799,19 @@
         <v>90</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>78</v>
@@ -21835,7 +21860,7 @@
         <v>78</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
@@ -21862,15 +21887,15 @@
         <v>78</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>312</v>
+        <v>266</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21884,7 +21909,7 @@
         <v>89</v>
       </c>
       <c r="H164" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I164" t="s" s="2">
         <v>78</v>
@@ -21893,18 +21918,20 @@
         <v>90</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>277</v>
+        <v>103</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>663</v>
+        <v>307</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>664</v>
+        <v>308</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="O164" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P164" t="s" s="2">
         <v>78</v>
       </c>
@@ -21928,11 +21955,13 @@
         <v>78</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="Y164" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y164" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z164" t="s" s="2">
-        <v>666</v>
+        <v>78</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>78</v>
@@ -21950,7 +21979,7 @@
         <v>78</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>662</v>
+        <v>311</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>79</v>
@@ -21968,7 +21997,7 @@
         <v>78</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>667</v>
+        <v>78</v>
       </c>
       <c r="AM164" t="s" s="2">
         <v>78</v>
@@ -21977,10 +22006,10 @@
         <v>78</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>78</v>
+        <v>312</v>
       </c>
     </row>
-    <row r="165" hidden="true">
+    <row r="165">
       <c r="A165" t="s" s="2">
         <v>668</v>
       </c>
@@ -21999,24 +22028,26 @@
         <v>89</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J165" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>103</v>
+        <v>277</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>104</v>
+        <v>669</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N165" s="2"/>
+        <v>670</v>
+      </c>
+      <c r="N165" t="s" s="2">
+        <v>671</v>
+      </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
         <v>78</v>
@@ -22041,13 +22072,11 @@
         <v>78</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y165" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="Y165" s="2"/>
       <c r="Z165" t="s" s="2">
-        <v>78</v>
+        <v>672</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>78</v>
@@ -22065,7 +22094,7 @@
         <v>78</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>106</v>
+        <v>668</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
@@ -22077,13 +22106,13 @@
         <v>78</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK165" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>78</v>
+        <v>673</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>78</v>
@@ -22097,21 +22126,21 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>78</v>
@@ -22123,17 +22152,15 @@
         <v>78</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N166" s="2"/>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
         <v>78</v>
@@ -22170,31 +22197,31 @@
         <v>78</v>
       </c>
       <c r="AB166" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC166" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD166" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE166" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH166" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI166" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>78</v>
@@ -22214,14 +22241,14 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
@@ -22237,23 +22264,21 @@
         <v>78</v>
       </c>
       <c r="J167" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>671</v>
+        <v>110</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>672</v>
+        <v>111</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
         <v>78</v>
       </c>
@@ -22289,19 +22314,19 @@
         <v>78</v>
       </c>
       <c r="AB167" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC167" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD167" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE167" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>287</v>
+        <v>116</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -22313,7 +22338,7 @@
         <v>78</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>78</v>
@@ -22328,15 +22353,15 @@
         <v>78</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22347,7 +22372,7 @@
         <v>79</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>78</v>
@@ -22356,19 +22381,23 @@
         <v>78</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>104</v>
+        <v>677</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N168" s="2"/>
-      <c r="O168" s="2"/>
+        <v>678</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O168" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P168" t="s" s="2">
         <v>78</v>
       </c>
@@ -22416,19 +22445,19 @@
         <v>78</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>106</v>
+        <v>287</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI168" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK168" t="s" s="2">
         <v>78</v>
@@ -22443,26 +22472,26 @@
         <v>78</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>78</v>
+        <v>288</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G169" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H169" t="s" s="2">
         <v>78</v>
@@ -22474,17 +22503,15 @@
         <v>78</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N169" s="2"/>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
         <v>78</v>
@@ -22521,31 +22548,31 @@
         <v>78</v>
       </c>
       <c r="AB169" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC169" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD169" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE169" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH169" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI169" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK169" t="s" s="2">
         <v>78</v>
@@ -22563,48 +22590,46 @@
         <v>78</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G170" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H170" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I170" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J170" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
         <v>78</v>
       </c>
@@ -22613,7 +22638,7 @@
         <v>78</v>
       </c>
       <c r="S170" t="s" s="2">
-        <v>676</v>
+        <v>78</v>
       </c>
       <c r="T170" t="s" s="2">
         <v>78</v>
@@ -22640,31 +22665,31 @@
         <v>78</v>
       </c>
       <c r="AB170" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC170" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD170" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE170" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>235</v>
+        <v>116</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH170" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI170" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK170" t="s" s="2">
         <v>78</v>
@@ -22679,15 +22704,15 @@
         <v>78</v>
       </c>
       <c r="AO170" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="171" hidden="true">
+    <row r="171">
       <c r="A171" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22701,7 +22726,7 @@
         <v>89</v>
       </c>
       <c r="H171" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I171" t="s" s="2">
         <v>78</v>
@@ -22710,18 +22735,20 @@
         <v>90</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O171" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="O171" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P171" t="s" s="2">
         <v>78</v>
       </c>
@@ -22730,7 +22757,7 @@
         <v>78</v>
       </c>
       <c r="S171" t="s" s="2">
-        <v>78</v>
+        <v>682</v>
       </c>
       <c r="T171" t="s" s="2">
         <v>78</v>
@@ -22769,7 +22796,7 @@
         <v>78</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>79</v>
@@ -22796,15 +22823,15 @@
         <v>78</v>
       </c>
       <c r="AO171" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22818,7 +22845,7 @@
         <v>89</v>
       </c>
       <c r="H172" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I172" t="s" s="2">
         <v>78</v>
@@ -22827,18 +22854,18 @@
         <v>90</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N172" s="2"/>
-      <c r="O172" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N172" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>78</v>
       </c>
@@ -22886,7 +22913,7 @@
         <v>78</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>79</v>
@@ -22913,15 +22940,15 @@
         <v>78</v>
       </c>
       <c r="AO172" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
-    <row r="173" hidden="true">
+    <row r="173">
       <c r="A173" t="s" s="2">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22935,7 +22962,7 @@
         <v>89</v>
       </c>
       <c r="H173" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I173" t="s" s="2">
         <v>78</v>
@@ -22944,17 +22971,17 @@
         <v>90</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>78</v>
@@ -23003,7 +23030,7 @@
         <v>78</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>79</v>
@@ -23030,15 +23057,15 @@
         <v>78</v>
       </c>
       <c r="AO173" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23061,19 +23088,17 @@
         <v>90</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>260</v>
+        <v>103</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N174" s="2"/>
       <c r="O174" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>78</v>
@@ -23122,7 +23147,7 @@
         <v>78</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>79</v>
@@ -23149,15 +23174,15 @@
         <v>78</v>
       </c>
       <c r="AO174" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23180,19 +23205,19 @@
         <v>90</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>78</v>
@@ -23241,7 +23266,7 @@
         <v>78</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>79</v>
@@ -23268,15 +23293,15 @@
         <v>78</v>
       </c>
       <c r="AO175" t="s" s="2">
-        <v>312</v>
+        <v>266</v>
       </c>
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23287,7 +23312,7 @@
         <v>79</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>78</v>
@@ -23296,21 +23321,23 @@
         <v>78</v>
       </c>
       <c r="J176" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>683</v>
+        <v>103</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>684</v>
+        <v>307</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>685</v>
+        <v>308</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="O176" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O176" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P176" t="s" s="2">
         <v>78</v>
       </c>
@@ -23358,13 +23385,13 @@
         <v>78</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>682</v>
+        <v>311</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>78</v>
@@ -23385,15 +23412,15 @@
         <v>78</v>
       </c>
       <c r="AO176" t="s" s="2">
-        <v>78</v>
+        <v>312</v>
       </c>
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23407,7 +23434,7 @@
         <v>80</v>
       </c>
       <c r="H177" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I177" t="s" s="2">
         <v>78</v>
@@ -23416,16 +23443,16 @@
         <v>78</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>277</v>
+        <v>689</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -23451,29 +23478,31 @@
         <v>78</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>691</v>
+        <v>78</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>692</v>
+        <v>78</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB177" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AC177" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC177" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD177" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE177" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>79</v>
@@ -23491,28 +23520,26 @@
         <v>78</v>
       </c>
       <c r="AL177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO177" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="178" hidden="true">
+      <c r="A178" t="s" s="2">
         <v>693</v>
       </c>
-      <c r="AM177" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN177" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO177" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s" s="2">
-        <v>694</v>
-      </c>
       <c r="B178" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="C178" t="s" s="2">
-        <v>695</v>
-      </c>
+        <v>693</v>
+      </c>
+      <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
         <v>78</v>
       </c>
@@ -23536,13 +23563,13 @@
         <v>277</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -23568,29 +23595,29 @@
         <v>78</v>
       </c>
       <c r="X178" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="Y178" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="Y178" t="s" s="2">
+        <v>697</v>
+      </c>
       <c r="Z178" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB178" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC178" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="AC178" s="2"/>
       <c r="AD178" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE178" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
@@ -23608,7 +23635,7 @@
         <v>78</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>78</v>
+        <v>699</v>
       </c>
       <c r="AM178" t="s" s="2">
         <v>78</v>
@@ -23620,14 +23647,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="179" hidden="true">
+    <row r="179">
       <c r="A179" t="s" s="2">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="C179" s="2"/>
+        <v>693</v>
+      </c>
+      <c r="C179" t="s" s="2">
+        <v>701</v>
+      </c>
       <c r="D179" t="s" s="2">
         <v>78</v>
       </c>
@@ -23636,10 +23665,10 @@
         <v>79</v>
       </c>
       <c r="G179" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H179" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I179" t="s" s="2">
         <v>78</v>
@@ -23648,15 +23677,17 @@
         <v>78</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>103</v>
+        <v>277</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>104</v>
+        <v>694</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N179" s="2"/>
+        <v>695</v>
+      </c>
+      <c r="N179" t="s" s="2">
+        <v>696</v>
+      </c>
       <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
         <v>78</v>
@@ -23681,13 +23712,11 @@
         <v>78</v>
       </c>
       <c r="X179" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y179" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="Y179" s="2"/>
       <c r="Z179" t="s" s="2">
-        <v>78</v>
+        <v>702</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>78</v>
@@ -23705,19 +23734,19 @@
         <v>78</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>106</v>
+        <v>693</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH179" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI179" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK179" t="s" s="2">
         <v>78</v>
@@ -23737,21 +23766,21 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G180" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H180" t="s" s="2">
         <v>78</v>
@@ -23763,17 +23792,15 @@
         <v>78</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N180" s="2"/>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
         <v>78</v>
@@ -23810,31 +23837,31 @@
         <v>78</v>
       </c>
       <c r="AB180" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC180" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD180" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE180" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH180" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI180" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ180" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK180" t="s" s="2">
         <v>78</v>
@@ -23854,14 +23881,14 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
@@ -23877,23 +23904,21 @@
         <v>78</v>
       </c>
       <c r="J181" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>703</v>
+        <v>110</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>704</v>
+        <v>111</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O181" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
         <v>78</v>
       </c>
@@ -23929,19 +23954,19 @@
         <v>78</v>
       </c>
       <c r="AB181" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC181" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD181" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE181" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>287</v>
+        <v>116</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>79</v>
@@ -23953,7 +23978,7 @@
         <v>78</v>
       </c>
       <c r="AJ181" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK181" t="s" s="2">
         <v>78</v>
@@ -23968,15 +23993,15 @@
         <v>78</v>
       </c>
       <c r="AO181" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23987,7 +24012,7 @@
         <v>79</v>
       </c>
       <c r="G182" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H182" t="s" s="2">
         <v>78</v>
@@ -23996,19 +24021,23 @@
         <v>78</v>
       </c>
       <c r="J182" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>104</v>
+        <v>709</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N182" s="2"/>
-      <c r="O182" s="2"/>
+        <v>710</v>
+      </c>
+      <c r="N182" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O182" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P182" t="s" s="2">
         <v>78</v>
       </c>
@@ -24056,19 +24085,19 @@
         <v>78</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>106</v>
+        <v>287</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH182" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI182" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ182" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK182" t="s" s="2">
         <v>78</v>
@@ -24083,26 +24112,26 @@
         <v>78</v>
       </c>
       <c r="AO182" t="s" s="2">
-        <v>78</v>
+        <v>288</v>
       </c>
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G183" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H183" t="s" s="2">
         <v>78</v>
@@ -24114,17 +24143,15 @@
         <v>78</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N183" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N183" s="2"/>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
         <v>78</v>
@@ -24161,31 +24188,31 @@
         <v>78</v>
       </c>
       <c r="AB183" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC183" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD183" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE183" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH183" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI183" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ183" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK183" t="s" s="2">
         <v>78</v>
@@ -24205,21 +24232,21 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E184" s="2"/>
       <c r="F184" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G184" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H184" t="s" s="2">
         <v>78</v>
@@ -24228,23 +24255,21 @@
         <v>78</v>
       </c>
       <c r="J184" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O184" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
         <v>78</v>
       </c>
@@ -24253,7 +24278,7 @@
         <v>78</v>
       </c>
       <c r="S184" t="s" s="2">
-        <v>711</v>
+        <v>78</v>
       </c>
       <c r="T184" t="s" s="2">
         <v>78</v>
@@ -24280,31 +24305,31 @@
         <v>78</v>
       </c>
       <c r="AB184" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC184" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD184" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE184" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>235</v>
+        <v>116</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH184" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI184" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ184" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK184" t="s" s="2">
         <v>78</v>
@@ -24319,15 +24344,15 @@
         <v>78</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24350,18 +24375,20 @@
         <v>90</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O185" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="O185" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P185" t="s" s="2">
         <v>78</v>
       </c>
@@ -24370,7 +24397,7 @@
         <v>78</v>
       </c>
       <c r="S185" t="s" s="2">
-        <v>78</v>
+        <v>717</v>
       </c>
       <c r="T185" t="s" s="2">
         <v>78</v>
@@ -24409,7 +24436,7 @@
         <v>78</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>79</v>
@@ -24436,15 +24463,15 @@
         <v>78</v>
       </c>
       <c r="AO185" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24452,13 +24479,13 @@
       </c>
       <c r="E186" s="2"/>
       <c r="F186" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G186" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H186" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I186" t="s" s="2">
         <v>78</v>
@@ -24467,18 +24494,18 @@
         <v>90</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N186" s="2"/>
-      <c r="O186" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N186" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O186" s="2"/>
       <c r="P186" t="s" s="2">
         <v>78</v>
       </c>
@@ -24526,7 +24553,7 @@
         <v>78</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>79</v>
@@ -24553,15 +24580,15 @@
         <v>78</v>
       </c>
       <c r="AO186" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
-    <row r="187" hidden="true">
+    <row r="187">
       <c r="A187" t="s" s="2">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24569,13 +24596,13 @@
       </c>
       <c r="E187" s="2"/>
       <c r="F187" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G187" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H187" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I187" t="s" s="2">
         <v>78</v>
@@ -24584,17 +24611,17 @@
         <v>90</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>78</v>
@@ -24643,7 +24670,7 @@
         <v>78</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -24670,15 +24697,15 @@
         <v>78</v>
       </c>
       <c r="AO187" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24701,19 +24728,17 @@
         <v>90</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>260</v>
+        <v>103</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N188" s="2"/>
       <c r="O188" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>78</v>
@@ -24762,7 +24787,7 @@
         <v>78</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -24789,15 +24814,15 @@
         <v>78</v>
       </c>
       <c r="AO188" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -24820,19 +24845,19 @@
         <v>90</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="O189" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>78</v>
@@ -24881,7 +24906,7 @@
         <v>78</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>79</v>
@@ -24908,19 +24933,17 @@
         <v>78</v>
       </c>
       <c r="AO189" t="s" s="2">
-        <v>312</v>
+        <v>266</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="C190" t="s" s="2">
-        <v>723</v>
-      </c>
+        <v>727</v>
+      </c>
+      <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
         <v>78</v>
       </c>
@@ -24929,30 +24952,32 @@
         <v>79</v>
       </c>
       <c r="G190" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J190" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I190" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J190" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K190" t="s" s="2">
-        <v>277</v>
+        <v>103</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>688</v>
+        <v>307</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>689</v>
+        <v>308</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="O190" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O190" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P190" t="s" s="2">
         <v>78</v>
       </c>
@@ -24976,11 +25001,13 @@
         <v>78</v>
       </c>
       <c r="X190" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="Y190" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y190" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z190" t="s" s="2">
-        <v>724</v>
+        <v>78</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>78</v>
@@ -24998,13 +25025,13 @@
         <v>78</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>687</v>
+        <v>311</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH190" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI190" t="s" s="2">
         <v>78</v>
@@ -25025,17 +25052,19 @@
         <v>78</v>
       </c>
       <c r="AO190" t="s" s="2">
-        <v>78</v>
+        <v>312</v>
       </c>
     </row>
-    <row r="191" hidden="true">
+    <row r="191">
       <c r="A191" t="s" s="2">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="C191" s="2"/>
+        <v>693</v>
+      </c>
+      <c r="C191" t="s" s="2">
+        <v>729</v>
+      </c>
       <c r="D191" t="s" s="2">
         <v>78</v>
       </c>
@@ -25044,10 +25073,10 @@
         <v>79</v>
       </c>
       <c r="G191" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H191" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I191" t="s" s="2">
         <v>78</v>
@@ -25056,15 +25085,17 @@
         <v>78</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>103</v>
+        <v>277</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>104</v>
+        <v>694</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N191" s="2"/>
+        <v>695</v>
+      </c>
+      <c r="N191" t="s" s="2">
+        <v>696</v>
+      </c>
       <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
         <v>78</v>
@@ -25089,13 +25120,11 @@
         <v>78</v>
       </c>
       <c r="X191" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y191" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="Y191" s="2"/>
       <c r="Z191" t="s" s="2">
-        <v>78</v>
+        <v>730</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>78</v>
@@ -25113,19 +25142,19 @@
         <v>78</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>106</v>
+        <v>693</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH191" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI191" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK191" t="s" s="2">
         <v>78</v>
@@ -25145,21 +25174,21 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E192" s="2"/>
       <c r="F192" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G192" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H192" t="s" s="2">
         <v>78</v>
@@ -25171,17 +25200,15 @@
         <v>78</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N192" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N192" s="2"/>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
         <v>78</v>
@@ -25218,31 +25245,31 @@
         <v>78</v>
       </c>
       <c r="AB192" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC192" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD192" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE192" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH192" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI192" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ192" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK192" t="s" s="2">
         <v>78</v>
@@ -25262,14 +25289,14 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
@@ -25285,23 +25312,21 @@
         <v>78</v>
       </c>
       <c r="J193" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>728</v>
+        <v>110</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>729</v>
+        <v>111</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O193" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
         <v>78</v>
       </c>
@@ -25337,19 +25362,19 @@
         <v>78</v>
       </c>
       <c r="AB193" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC193" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD193" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE193" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>287</v>
+        <v>116</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>79</v>
@@ -25361,7 +25386,7 @@
         <v>78</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK193" t="s" s="2">
         <v>78</v>
@@ -25376,15 +25401,15 @@
         <v>78</v>
       </c>
       <c r="AO193" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -25395,7 +25420,7 @@
         <v>79</v>
       </c>
       <c r="G194" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H194" t="s" s="2">
         <v>78</v>
@@ -25404,19 +25429,23 @@
         <v>78</v>
       </c>
       <c r="J194" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>104</v>
+        <v>734</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N194" s="2"/>
-      <c r="O194" s="2"/>
+        <v>735</v>
+      </c>
+      <c r="N194" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O194" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P194" t="s" s="2">
         <v>78</v>
       </c>
@@ -25464,19 +25493,19 @@
         <v>78</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>106</v>
+        <v>287</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH194" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI194" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ194" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK194" t="s" s="2">
         <v>78</v>
@@ -25491,26 +25520,26 @@
         <v>78</v>
       </c>
       <c r="AO194" t="s" s="2">
-        <v>78</v>
+        <v>288</v>
       </c>
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G195" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H195" t="s" s="2">
         <v>78</v>
@@ -25522,17 +25551,15 @@
         <v>78</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N195" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N195" s="2"/>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
         <v>78</v>
@@ -25569,31 +25596,31 @@
         <v>78</v>
       </c>
       <c r="AB195" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC195" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD195" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE195" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH195" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI195" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ195" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK195" t="s" s="2">
         <v>78</v>
@@ -25613,21 +25640,21 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E196" s="2"/>
       <c r="F196" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G196" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H196" t="s" s="2">
         <v>78</v>
@@ -25636,23 +25663,21 @@
         <v>78</v>
       </c>
       <c r="J196" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O196" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
         <v>78</v>
       </c>
@@ -25661,7 +25686,7 @@
         <v>78</v>
       </c>
       <c r="S196" t="s" s="2">
-        <v>733</v>
+        <v>78</v>
       </c>
       <c r="T196" t="s" s="2">
         <v>78</v>
@@ -25688,31 +25713,31 @@
         <v>78</v>
       </c>
       <c r="AB196" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC196" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD196" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE196" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>235</v>
+        <v>116</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH196" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI196" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ196" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK196" t="s" s="2">
         <v>78</v>
@@ -25727,15 +25752,15 @@
         <v>78</v>
       </c>
       <c r="AO196" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -25743,7 +25768,7 @@
       </c>
       <c r="E197" s="2"/>
       <c r="F197" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G197" t="s" s="2">
         <v>89</v>
@@ -25758,18 +25783,20 @@
         <v>90</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O197" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="O197" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P197" t="s" s="2">
         <v>78</v>
       </c>
@@ -25778,7 +25805,7 @@
         <v>78</v>
       </c>
       <c r="S197" t="s" s="2">
-        <v>78</v>
+        <v>739</v>
       </c>
       <c r="T197" t="s" s="2">
         <v>78</v>
@@ -25817,7 +25844,7 @@
         <v>78</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>79</v>
@@ -25844,15 +25871,15 @@
         <v>78</v>
       </c>
       <c r="AO197" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -25860,7 +25887,7 @@
       </c>
       <c r="E198" s="2"/>
       <c r="F198" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G198" t="s" s="2">
         <v>89</v>
@@ -25875,18 +25902,18 @@
         <v>90</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N198" s="2"/>
-      <c r="O198" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N198" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
         <v>78</v>
       </c>
@@ -25934,7 +25961,7 @@
         <v>78</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>79</v>
@@ -25961,15 +25988,15 @@
         <v>78</v>
       </c>
       <c r="AO198" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -25977,7 +26004,7 @@
       </c>
       <c r="E199" s="2"/>
       <c r="F199" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G199" t="s" s="2">
         <v>89</v>
@@ -25992,17 +26019,17 @@
         <v>90</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="N199" s="2"/>
       <c r="O199" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>78</v>
@@ -26051,7 +26078,7 @@
         <v>78</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>79</v>
@@ -26078,15 +26105,15 @@
         <v>78</v>
       </c>
       <c r="AO199" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26109,19 +26136,17 @@
         <v>90</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>260</v>
+        <v>103</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N200" s="2"/>
       <c r="O200" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>78</v>
@@ -26170,7 +26195,7 @@
         <v>78</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>79</v>
@@ -26197,15 +26222,15 @@
         <v>78</v>
       </c>
       <c r="AO200" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26228,19 +26253,19 @@
         <v>90</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>78</v>
@@ -26289,7 +26314,7 @@
         <v>78</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>79</v>
@@ -26316,15 +26341,15 @@
         <v>78</v>
       </c>
       <c r="AO201" t="s" s="2">
-        <v>312</v>
+        <v>266</v>
       </c>
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>739</v>
+        <v>727</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -26335,7 +26360,7 @@
         <v>79</v>
       </c>
       <c r="G202" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H202" t="s" s="2">
         <v>78</v>
@@ -26344,20 +26369,22 @@
         <v>78</v>
       </c>
       <c r="J202" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>740</v>
+        <v>103</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>741</v>
+        <v>307</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="N202" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N202" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="O202" t="s" s="2">
-        <v>743</v>
+        <v>310</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>78</v>
@@ -26406,13 +26433,13 @@
         <v>78</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>739</v>
+        <v>311</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH202" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI202" t="s" s="2">
         <v>78</v>
@@ -26433,15 +26460,15 @@
         <v>78</v>
       </c>
       <c r="AO202" t="s" s="2">
-        <v>78</v>
+        <v>312</v>
       </c>
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -26464,16 +26491,18 @@
         <v>78</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>277</v>
+        <v>746</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N203" s="2"/>
-      <c r="O203" s="2"/>
+      <c r="O203" t="s" s="2">
+        <v>749</v>
+      </c>
       <c r="P203" t="s" s="2">
         <v>78</v>
       </c>
@@ -26497,13 +26526,13 @@
         <v>78</v>
       </c>
       <c r="X203" t="s" s="2">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="Y203" t="s" s="2">
-        <v>747</v>
+        <v>78</v>
       </c>
       <c r="Z203" t="s" s="2">
-        <v>748</v>
+        <v>78</v>
       </c>
       <c r="AA203" t="s" s="2">
         <v>78</v>
@@ -26521,7 +26550,7 @@
         <v>78</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>79</v>
@@ -26551,12 +26580,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -26570,7 +26599,7 @@
         <v>80</v>
       </c>
       <c r="H204" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I204" t="s" s="2">
         <v>78</v>
@@ -26579,7 +26608,7 @@
         <v>78</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>750</v>
+        <v>277</v>
       </c>
       <c r="L204" t="s" s="2">
         <v>751</v>
@@ -26612,13 +26641,13 @@
         <v>78</v>
       </c>
       <c r="X204" t="s" s="2">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="Y204" t="s" s="2">
-        <v>78</v>
+        <v>753</v>
       </c>
       <c r="Z204" t="s" s="2">
-        <v>78</v>
+        <v>754</v>
       </c>
       <c r="AA204" t="s" s="2">
         <v>78</v>
@@ -26636,7 +26665,7 @@
         <v>78</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>79</v>
@@ -26657,16 +26686,16 @@
         <v>78</v>
       </c>
       <c r="AM204" t="s" s="2">
-        <v>753</v>
+        <v>78</v>
       </c>
       <c r="AN204" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO204" t="s" s="2">
-        <v>754</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="205" hidden="true">
+    <row r="205">
       <c r="A205" t="s" s="2">
         <v>755</v>
       </c>
@@ -26685,7 +26714,7 @@
         <v>80</v>
       </c>
       <c r="H205" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I205" t="s" s="2">
         <v>78</v>
@@ -26694,13 +26723,13 @@
         <v>78</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>582</v>
+        <v>756</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>
@@ -26772,21 +26801,21 @@
         <v>78</v>
       </c>
       <c r="AM205" t="s" s="2">
-        <v>78</v>
+        <v>759</v>
       </c>
       <c r="AN205" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO205" t="s" s="2">
-        <v>78</v>
+        <v>760</v>
       </c>
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -26797,7 +26826,7 @@
         <v>79</v>
       </c>
       <c r="G206" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H206" t="s" s="2">
         <v>78</v>
@@ -26809,13 +26838,13 @@
         <v>78</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>103</v>
+        <v>583</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>104</v>
+        <v>762</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>105</v>
+        <v>763</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
@@ -26866,19 +26895,19 @@
         <v>78</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>106</v>
+        <v>761</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH206" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI206" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ206" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK206" t="s" s="2">
         <v>78</v>
@@ -26898,21 +26927,21 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E207" s="2"/>
       <c r="F207" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G207" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H207" t="s" s="2">
         <v>78</v>
@@ -26924,17 +26953,15 @@
         <v>78</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N207" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N207" s="2"/>
       <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
         <v>78</v>
@@ -26983,19 +27010,19 @@
         <v>78</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH207" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI207" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ207" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK207" t="s" s="2">
         <v>78</v>
@@ -27015,14 +27042,14 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
-        <v>589</v>
+        <v>108</v>
       </c>
       <c r="E208" s="2"/>
       <c r="F208" t="s" s="2">
@@ -27035,26 +27062,24 @@
         <v>78</v>
       </c>
       <c r="I208" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J208" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K208" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>590</v>
+        <v>110</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>591</v>
+        <v>111</v>
       </c>
       <c r="N208" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="O208" t="s" s="2">
-        <v>339</v>
-      </c>
+      <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
         <v>78</v>
       </c>
@@ -27102,7 +27127,7 @@
         <v>78</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>592</v>
+        <v>116</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>79</v>
@@ -27134,42 +27159,46 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
-        <v>78</v>
+        <v>590</v>
       </c>
       <c r="E209" s="2"/>
       <c r="F209" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G209" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H209" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I209" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J209" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>277</v>
+        <v>109</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>762</v>
+        <v>591</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>763</v>
-      </c>
-      <c r="N209" s="2"/>
-      <c r="O209" s="2"/>
+        <v>592</v>
+      </c>
+      <c r="N209" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O209" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="P209" t="s" s="2">
         <v>78</v>
       </c>
@@ -27193,13 +27222,13 @@
         <v>78</v>
       </c>
       <c r="X209" t="s" s="2">
-        <v>168</v>
+        <v>78</v>
       </c>
       <c r="Y209" t="s" s="2">
-        <v>764</v>
+        <v>78</v>
       </c>
       <c r="Z209" t="s" s="2">
-        <v>765</v>
+        <v>78</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>78</v>
@@ -27217,19 +27246,19 @@
         <v>78</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>761</v>
+        <v>593</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH209" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI209" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ209" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK209" t="s" s="2">
         <v>78</v>
@@ -27249,10 +27278,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -27260,7 +27289,7 @@
       </c>
       <c r="E210" s="2"/>
       <c r="F210" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G210" t="s" s="2">
         <v>89</v>
@@ -27275,7 +27304,7 @@
         <v>78</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>767</v>
+        <v>277</v>
       </c>
       <c r="L210" t="s" s="2">
         <v>768</v>
@@ -27308,13 +27337,13 @@
         <v>78</v>
       </c>
       <c r="X210" t="s" s="2">
-        <v>78</v>
+        <v>168</v>
       </c>
       <c r="Y210" t="s" s="2">
-        <v>78</v>
+        <v>770</v>
       </c>
       <c r="Z210" t="s" s="2">
-        <v>78</v>
+        <v>771</v>
       </c>
       <c r="AA210" t="s" s="2">
         <v>78</v>
@@ -27332,10 +27361,10 @@
         <v>78</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AG210" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH210" t="s" s="2">
         <v>89</v>
@@ -27364,10 +27393,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -27375,10 +27404,10 @@
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G211" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H211" t="s" s="2">
         <v>78</v>
@@ -27390,20 +27419,16 @@
         <v>78</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>773</v>
-      </c>
-      <c r="N211" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="O211" t="s" s="2">
         <v>775</v>
       </c>
+      <c r="N211" s="2"/>
+      <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
         <v>78</v>
       </c>
@@ -27451,13 +27476,13 @@
         <v>78</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="AG211" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH211" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI211" t="s" s="2">
         <v>78</v>
@@ -27481,7 +27506,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
         <v>776</v>
       </c>
@@ -27500,7 +27525,7 @@
         <v>80</v>
       </c>
       <c r="H212" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I212" t="s" s="2">
         <v>78</v>
@@ -27509,18 +27534,20 @@
         <v>78</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>277</v>
+        <v>777</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="O212" s="2"/>
+        <v>780</v>
+      </c>
+      <c r="O212" t="s" s="2">
+        <v>781</v>
+      </c>
       <c r="P212" t="s" s="2">
         <v>78</v>
       </c>
@@ -27544,13 +27571,13 @@
         <v>78</v>
       </c>
       <c r="X212" t="s" s="2">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="Y212" t="s" s="2">
-        <v>779</v>
+        <v>78</v>
       </c>
       <c r="Z212" t="s" s="2">
-        <v>780</v>
+        <v>78</v>
       </c>
       <c r="AA212" t="s" s="2">
         <v>78</v>
@@ -27598,12 +27625,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="213" hidden="true">
+    <row r="213">
       <c r="A213" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -27614,10 +27641,10 @@
         <v>79</v>
       </c>
       <c r="G213" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H213" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I213" t="s" s="2">
         <v>78</v>
@@ -27626,15 +27653,17 @@
         <v>78</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>103</v>
+        <v>277</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>104</v>
+        <v>783</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N213" s="2"/>
+        <v>784</v>
+      </c>
+      <c r="N213" t="s" s="2">
+        <v>780</v>
+      </c>
       <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
         <v>78</v>
@@ -27659,13 +27688,13 @@
         <v>78</v>
       </c>
       <c r="X213" t="s" s="2">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="Y213" t="s" s="2">
-        <v>78</v>
+        <v>785</v>
       </c>
       <c r="Z213" t="s" s="2">
-        <v>78</v>
+        <v>786</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>78</v>
@@ -27683,19 +27712,19 @@
         <v>78</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>106</v>
+        <v>782</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH213" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI213" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ213" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK213" t="s" s="2">
         <v>78</v>
@@ -27715,21 +27744,21 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E214" s="2"/>
       <c r="F214" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G214" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H214" t="s" s="2">
         <v>78</v>
@@ -27741,17 +27770,15 @@
         <v>78</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N214" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N214" s="2"/>
       <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
         <v>78</v>
@@ -27788,31 +27815,31 @@
         <v>78</v>
       </c>
       <c r="AB214" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC214" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD214" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE214" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH214" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI214" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ214" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK214" t="s" s="2">
         <v>78</v>
@@ -27832,14 +27859,14 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E215" s="2"/>
       <c r="F215" t="s" s="2">
@@ -27849,29 +27876,27 @@
         <v>80</v>
       </c>
       <c r="H215" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I215" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J215" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>283</v>
+        <v>110</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>284</v>
+        <v>111</v>
       </c>
       <c r="N215" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O215" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
         <v>78</v>
       </c>
@@ -27907,10 +27932,10 @@
         <v>78</v>
       </c>
       <c r="AB215" t="s" s="2">
-        <v>784</v>
+        <v>113</v>
       </c>
       <c r="AC215" t="s" s="2">
-        <v>785</v>
+        <v>114</v>
       </c>
       <c r="AD215" t="s" s="2">
         <v>78</v>
@@ -27919,7 +27944,7 @@
         <v>115</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>287</v>
+        <v>116</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>79</v>
@@ -27931,7 +27956,7 @@
         <v>78</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK215" t="s" s="2">
         <v>78</v>
@@ -27946,15 +27971,15 @@
         <v>78</v>
       </c>
       <c r="AO215" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -27965,10 +27990,10 @@
         <v>79</v>
       </c>
       <c r="G216" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H216" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I216" t="s" s="2">
         <v>78</v>
@@ -27977,19 +28002,19 @@
         <v>90</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="O216" t="s" s="2">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>78</v>
@@ -28026,25 +28051,25 @@
         <v>78</v>
       </c>
       <c r="AB216" t="s" s="2">
-        <v>78</v>
+        <v>790</v>
       </c>
       <c r="AC216" t="s" s="2">
-        <v>78</v>
+        <v>791</v>
       </c>
       <c r="AD216" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE216" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>311</v>
+        <v>287</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH216" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI216" t="s" s="2">
         <v>78</v>
@@ -28065,11 +28090,130 @@
         <v>78</v>
       </c>
       <c r="AO216" t="s" s="2">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="217" hidden="true">
+      <c r="A217" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="B217" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="C217" s="2"/>
+      <c r="D217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E217" s="2"/>
+      <c r="F217" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G217" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J217" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K217" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L217" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M217" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N217" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O217" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="P217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q217" s="2"/>
+      <c r="R217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF217" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AG217" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH217" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ217" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO217" t="s" s="2">
         <v>312</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO216">
+  <autoFilter ref="A1:AO217">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -28079,7 +28223,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI215">
+  <conditionalFormatting sqref="A2:AI216">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:38:11+00:00</t>
+    <t>2026-09-01T21:24:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-operation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:24:42+00:00</t>
+    <t>2026-09-01T22:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
